--- a/Aii竞彩推荐_2026-05-12.xlsx
+++ b/Aii竞彩推荐_2026-05-12.xlsx
@@ -94,7 +94,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -116,11 +116,55 @@
         <color rgb="00D0D0D0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -154,6 +198,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -519,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -544,7 +593,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 11:28</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 11:58</t>
         </is>
       </c>
     </row>
@@ -659,7 +708,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP2.49/2.80/2.70 让球-1</t>
+          <t>SP6.25/3.85/1.41 让球-1</t>
         </is>
       </c>
     </row>
@@ -706,7 +755,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>SP7.70/4.15/1.32 让球+1</t>
+          <t>SP2.88/3.30/2.09 让球+1</t>
         </is>
       </c>
     </row>
@@ -753,7 +802,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP1.67/3.60/3.95 让球-1</t>
+          <t>SP3.10/3.50/1.92 让球-1</t>
         </is>
       </c>
     </row>
@@ -770,17 +819,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>利雅胜利</t>
+          <t>利雅得胜利</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>利雅新月</t>
+          <t>利雅得新月</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>沙职</t>
+          <t>沙特职业联赛</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -800,7 +849,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>SP1.98/3.70/2.82 让球-1</t>
+          <t>SP3.76/4.00/1.63 让球-1</t>
         </is>
       </c>
     </row>
@@ -847,7 +896,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>SP1.46/4.10/5.00 让球-1</t>
+          <t>SP2.50/3.40/2.30 让球-1</t>
         </is>
       </c>
     </row>
@@ -894,7 +943,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>SP1.95/3.15/3.35 让球-1</t>
+          <t>SP4.15/3.55/1.65 让球-1</t>
         </is>
       </c>
     </row>
@@ -941,7 +990,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>SP2.20/3.22/2.75 让球-1</t>
+          <t>SP4.60/4.08/1.50 让球-1</t>
         </is>
       </c>
     </row>
@@ -988,14 +1037,14 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>SP2.18/3.30/2.72 让球-1</t>
+          <t>SP4.65/3.90/1.52 让球-1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 11:28）</t>
+          <t>📊 竞彩SP数据（含真实让球SP · 11:58）</t>
         </is>
       </c>
     </row>
@@ -1068,13 +1117,13 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2.49</v>
+        <v>6.25</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>2.8</v>
+        <v>3.85</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>2.7</v>
+        <v>1.41</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
@@ -1083,17 +1132,17 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1163,13 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>7.7</v>
+        <v>2.88</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>1.32</v>
+        <v>2.09</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1129,17 +1178,17 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.31</t>
         </is>
       </c>
     </row>
@@ -1160,13 +1209,13 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>3.95</v>
+        <v>1.92</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
@@ -1175,17 +1224,17 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.95</t>
         </is>
       </c>
     </row>
@@ -1197,22 +1246,22 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>沙职</t>
+          <t>沙特职业联赛</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>利雅胜利vs利雅新月</t>
+          <t>利雅得胜利vs利雅得新月</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>1.98</v>
+        <v>3.76</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>2.82</v>
+        <v>1.63</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1221,17 +1270,17 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.82</t>
         </is>
       </c>
     </row>
@@ -1252,13 +1301,13 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>1.46</v>
+        <v>2.5</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
@@ -1267,17 +1316,17 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
@@ -1298,13 +1347,13 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>1.95</v>
+        <v>4.15</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>3.35</v>
+        <v>1.65</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1313,17 +1362,17 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>3.35</t>
         </is>
       </c>
     </row>
@@ -1344,13 +1393,13 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>3.22</v>
+        <v>4.08</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
@@ -1359,17 +1408,17 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
@@ -1390,13 +1439,13 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2.18</v>
+        <v>4.65</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>2.72</v>
+        <v>1.52</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1405,17 +1454,17 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.72</t>
         </is>
       </c>
     </row>
@@ -1491,32 +1540,32 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>负负</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>平负</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
@@ -1526,7 +1575,7 @@
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=40%P平=31%P客=30%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让胜</t>
+          <t>贝叶斯P主=31%P平=29%P客=40%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球-1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -1543,32 +1592,32 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
@@ -1578,7 +1627,7 @@
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=31%P平=28%P客=41%|泊松比分0-1|半全场负负|大小球小2.5(40%)|让球+1=输盘/让胜</t>
+          <t>贝叶斯P主=36%P平=30%P客=34%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球+1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -1595,32 +1644,32 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>负负</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>平负</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
@@ -1630,7 +1679,7 @@
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=44%P平=27%P客=29%|泊松比分2-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜</t>
+          <t>贝叶斯P主=34%P平=28%P客=38%|泊松比分1-2|半全场负负|大小球大2.5(69%)|让球-1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1691,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>利雅胜利vs利雅新月</t>
+          <t>利雅得胜利vs利雅得新月</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -1657,7 +1706,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -1667,12 +1716,12 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>负负</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>平负</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
@@ -1682,7 +1731,7 @@
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=43%P平=28%P客=29%|泊松比分1-0|半全场胜胜|大小球小2.5(45%)|让球-1=输盘/让胜</t>
+          <t>贝叶斯P主=33%P平=28%P客=39%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球-1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1783,7 @@
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=49%P平=26%P客=25%|泊松比分3-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜</t>
+          <t>贝叶斯P主=38%P平=28%P客=34%|泊松比分3-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
@@ -1751,32 +1800,32 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>负负</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>平负</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
@@ -1786,7 +1835,7 @@
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=43%P平=29%P客=28%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让胜</t>
+          <t>贝叶斯P主=32%P平=29%P客=39%|泊松比分0-1|半全场负负|大小球小2.5(40%)|让球-1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -1803,17 +1852,17 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -1823,12 +1872,12 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>负负</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>平负</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
@@ -1838,7 +1887,7 @@
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=43%P平=29%P客=28%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让胜</t>
+          <t>贝叶斯P主=35%P平=27%P客=38%|泊松比分1-3|半全场负负|大小球大2.5(70%)|让球-1=穿盘/让胜</t>
         </is>
       </c>
     </row>
@@ -1855,17 +1904,17 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>3/10</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -1875,12 +1924,12 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>负负</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>平负</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -1890,7 +1939,7 @@
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=41%P平=26%P客=33%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让胜</t>
+          <t>贝叶斯P主=29%P平=26%P客=45%|泊松比分1-3|半全场负负|大小球大2.5(70%)|让球-1=穿盘/让胜</t>
         </is>
       </c>
     </row>
@@ -2788,118 +2837,229 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>2串1</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>周二003+周二006</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>·塞尔塔:客胜(1.92)
+·圣旺红星:客胜(1.65)</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>1.92×1.65=3.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>3串1</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>周二003+周二006+周二007</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>·塞尔塔:客胜(1.92)
+·圣旺红星:客胜(1.65)
+·南安普敦:客胜(1.50)</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>1.92×1.65×1.50=4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>4串1</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>周二003+周二006+周二007+周二008</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>·塞尔塔:客胜(1.92)
+·圣旺红星:客胜(1.65)
+·南安普敦:客胜(1.50)
+·奥萨苏纳:客胜(1.52)</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>7.22</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>1.92×1.65×1.50×1.52=7.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>⚠️ 核心信号</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>信号</t>
         </is>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t>场次</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>解读</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>应对</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="9" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
         <is>
           <t>🟢 高信心(4/10+)</t>
         </is>
       </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>0场贝叶斯概率最高</t>
         </is>
       </c>
-      <c r="D84" s="6" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>作胆材/串关核心</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="9" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
         <is>
           <t>🟢 让球SP真实数据</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>全部场次</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>从500.com让球页提取，非估算</t>
         </is>
       </c>
-      <c r="D85" s="6" t="inlineStr">
+      <c r="D88" s="6" t="inlineStr">
         <is>
           <t>可用作让球分析</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="11" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="11" t="inlineStr">
         <is>
           <t>🟡 平局候选</t>
         </is>
       </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>周二001</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>1场平局概率30%+</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>0场平局概率30%+</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>双选或慎入</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="11" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="11" t="inlineStr">
         <is>
           <t>🟡 让球数真实</t>
         </is>
       </c>
-      <c r="B87" s="6" t="inlineStr">
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>全部场次</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>从500.com data-rangqiu提取</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
+      <c r="D90" s="6" t="inlineStr">
         <is>
           <t>让球分析可靠</t>
         </is>
@@ -2909,12 +3069,12 @@
   <mergeCells count="19">
     <mergeCell ref="A47:J47"/>
     <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A85:J85"/>
     <mergeCell ref="A72:J72"/>
     <mergeCell ref="A68:J68"/>
     <mergeCell ref="A67:J67"/>
     <mergeCell ref="A34:J34"/>
     <mergeCell ref="A73:J73"/>
-    <mergeCell ref="A82:J82"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A70:J70"/>
@@ -2963,11 +3123,11 @@
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：韩职
-竞彩SP：2.49 / 2.80 / 2.70
-让球SP(真实)：6.25/3.85/1.41
-差值分析：P主=40% P平=31% P客=30%
-推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
-让球:让-1 输盘=让胜 </t>
+竞彩SP：6.25 / 3.85 / 1.41
+让球SP(真实)：2.49/2.80/2.70
+差值分析：P主=31% P平=29% P客=40%
+推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
+让球:让-1 走水=让平 </t>
         </is>
       </c>
     </row>
@@ -2983,11 +3143,11 @@
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：韩职
-竞彩SP：7.70 / 4.15 / 1.32
-让球SP(真实)：2.81/3.25/2.15
-差值分析：P主=31% P平=28% P客=41%
-推荐：客胜 信心1/10 比分0-1(泊松) 半全场负负 大小球小2.5(40%) 备选半全场:平负
-让球:让+1 输盘=让胜 </t>
+竞彩SP：2.88 / 3.30 / 2.09
+让球SP(真实)：7.80/4.20/1.31
+差值分析：P主=36% P平=30% P客=34%
+推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
+让球:让+1 走水=让平 </t>
         </is>
       </c>
     </row>
@@ -3003,18 +3163,18 @@
         <is>
           <t xml:space="preserve">时间：01:00
 联赛：西甲
-竞彩SP：1.67 / 3.60 / 3.95
-让球SP(真实)：3.10/3.50/1.92
-差值分析：P主=44% P平=27% P客=29%
-推荐：主胜 信心1/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
-让球:让-1 输盘=让胜 </t>
+竞彩SP：3.10 / 3.50 / 1.92
+让球SP(真实)：1.67/3.60/3.95
+差值分析：P主=34% P平=28% P客=38%
+推荐：客胜 信心3/10 比分1-2(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:平负
+让球:让-1 走水=让平 </t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>⚽ 周二004 利雅胜利 vs 利雅新月 [沙职] 02:00</t>
+          <t>⚽ 周二004 利雅得胜利 vs 利雅得新月 [沙特职业联赛] 02:00</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3182,12 @@
       <c r="B28" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">时间：02:00
-联赛：沙职
-竞彩SP：1.98 / 3.70 / 2.82
-让球SP(真实)：3.76/4.00/1.63
-差值分析：P主=43% P平=28% P客=29%
-推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(45%) 备选半全场:平胜
-让球:让-1 输盘=让胜 </t>
+联赛：沙特职业联赛
+竞彩SP：3.76 / 4.00 / 1.63
+让球SP(真实)：1.98/3.70/2.82
+差值分析：P主=33% P平=28% P客=39%
+推荐：客胜 信心1/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
+让球:让-1 走水=让平 </t>
         </is>
       </c>
     </row>
@@ -3043,9 +3203,9 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：西甲
-竞彩SP：1.46 / 4.10 / 5.00
-让球SP(真实)：2.50/3.40/2.30
-差值分析：P主=49% P平=26% P客=25%
+竞彩SP：2.50 / 3.40 / 2.30
+让球SP(真实)：1.46/4.10/5.00
+差值分析：P主=38% P平=28% P客=34%
 推荐：主胜 信心2/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
@@ -3063,11 +3223,11 @@
         <is>
           <t xml:space="preserve">时间：02:30
 联赛：法甲
-竞彩SP：1.95 / 3.15 / 3.35
-让球SP(真实)：4.15/3.55/1.65
-差值分析：P主=43% P平=29% P客=28%
-推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
-让球:让-1 输盘=让胜 </t>
+竞彩SP：4.15 / 3.55 / 1.65
+让球SP(真实)：1.95/3.15/3.35
+差值分析：P主=32% P平=29% P客=39%
+推荐：客胜 信心3/10 比分0-1(泊松) 半全场负负 大小球小2.5(40%) 备选半全场:平负
+让球:让-1 走水=让平 </t>
         </is>
       </c>
     </row>
@@ -3083,11 +3243,11 @@
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：英冠
-竞彩SP：2.20 / 3.22 / 2.75
-让球SP(真实)：4.60/4.08/1.50
-差值分析：P主=43% P平=29% P客=28%
-推荐：主胜 信心1/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
-让球:让-1 输盘=让胜 </t>
+竞彩SP：4.60 / 4.08 / 1.50
+让球SP(真实)：2.20/3.22/2.75
+差值分析：P主=35% P平=27% P客=38%
+推荐：客胜 信心3/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
+让球:让-1 穿盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -3103,11 +3263,11 @@
         <is>
           <t xml:space="preserve">时间：03:30
 联赛：西甲
-竞彩SP：2.18 / 3.30 / 2.72
-让球SP(真实)：4.65/3.90/1.52
-差值分析：P主=41% P平=26% P客=33%
-推荐：主胜 信心1/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
-让球:让-1 输盘=让胜 </t>
+竞彩SP：4.65 / 3.90 / 1.52
+让球SP(真实)：2.18/3.30/2.72
+差值分析：P主=29% P平=26% P客=45%
+推荐：客胜 信心3/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
+让球:让-1 穿盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -3133,7 +3293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3202,6 +3362,132 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>2串1</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>周二003+周二006</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>·塞尔塔:客胜(1.92)
+·圣旺红星:客胜(1.65)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>6元</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>3.17倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>3串1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>周二003+周二006+周二007</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>·塞尔塔:客胜(1.92)
+·圣旺红星:客胜(1.65)
+·南安普敦:客胜(1.50)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>10元</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>4.75倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>4串1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>周二003+周二006+周二007+周二008</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>·塞尔塔:客胜(1.92)
+·圣旺红星:客胜(1.65)
+·南安普敦:客胜(1.50)
+·奥萨苏纳:客胜(1.52)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>7.22</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>14元</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>7.22倍</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
@@ -3209,10 +3495,177 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>2串1</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>比分</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>周二003+周二006</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>79.00</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>1元</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>79元</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>79.00倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>3串1</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>比分</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>周二003+周二006+周二007</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>594.00</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>1元</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>594元</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>594.00倍</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>C. 混合串关（胜平负+让球穿盘）</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="17" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>3串1</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>周二003+周二006+周二007</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>1元</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>5元</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>4.75倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>4串1</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>周二003+周二006+周二007+周二008</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>7.22</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>1元</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>7元</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>7.22倍</t>
         </is>
       </c>
     </row>
@@ -3220,6 +3673,126 @@
       <c r="A15" s="13" t="inlineStr">
         <is>
           <t>D. 半全场串关（从泊松比分推半全场）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>2串1</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>半全场</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>周二003+周二006</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>1元</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>6元</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>6.25倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>3串1</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>半全场</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>周二003+周二006+周二007</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>15.62</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>1元</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>16元</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>15.62倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>4串1</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>半全场</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>周二003+周二006+周二007+周二008</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>39.06</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>1元</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>39元</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>39.06倍</t>
         </is>
       </c>
     </row>

--- a/Aii竞彩推荐_2026-05-12.xlsx
+++ b/Aii竞彩推荐_2026-05-12.xlsx
@@ -593,7 +593,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 11:58</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 13:25</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP3.10/3.50/1.92 让球-1</t>
+          <t>SP3.10/3.40/1.95 让球-1</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>SP3.76/4.00/1.63 让球-1</t>
+          <t>SP3.87/4.00/1.61 让球-1</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>SP2.50/3.40/2.30 让球-1</t>
+          <t>SP2.50/3.30/2.35 让球-1</t>
         </is>
       </c>
     </row>
@@ -1037,14 +1037,14 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>SP4.65/3.90/1.52 让球-1</t>
+          <t>SP4.85/3.90/1.50 让球-1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>📊 竞彩SP数据（含真实让球SP · 11:58）</t>
+          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 13:25</t>
         </is>
       </c>
     </row>
@@ -1066,37 +1066,37 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>胜SP</t>
+          <t>欧赔胜</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>平SP</t>
+          <t>欧赔平</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>负SP</t>
+          <t>欧赔负</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>让球</t>
+          <t>让球数</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>让球SP胜</t>
+          <t>竞彩SP胜</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>让球SP平</t>
+          <t>竞彩SP平</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>让球SP负</t>
+          <t>竞彩SP负</t>
         </is>
       </c>
     </row>
@@ -1212,10 +1212,10 @@
         <v>3.1</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>3.76</v>
+        <v>3.87</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
@@ -1304,10 +1304,10 @@
         <v>2.5</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
@@ -1439,13 +1439,13 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>4.65</v>
+        <v>4.85</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>3.9</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1454,17 +1454,17 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.65</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=36%P平=30%P客=34%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球+1=走水/让平</t>
+          <t>贝叶斯P主=36%P平=30%P客=34%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球+1=走水/让平|赔变主↑2% 平↑2% 客↓3%</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=33%P平=28%P客=39%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球-1=走水/让平</t>
+          <t>贝叶斯P主=33%P平=28%P客=40%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球-1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>·塞尔塔:客胜(1.92)
+          <t>·塞尔塔:客胜(1.95)
 ·圣旺红星:客胜(1.65)</t>
         </is>
       </c>
@@ -2864,12 +2864,12 @@
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>1.92×1.65=3.17</t>
+          <t>1.95×1.65=3.22</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>·塞尔塔:客胜(1.92)
+          <t>·塞尔塔:客胜(1.95)
 ·圣旺红星:客胜(1.65)
 ·南安普敦:客胜(1.50)</t>
         </is>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>1.92×1.65×1.50=4.75</t>
+          <t>1.95×1.65×1.50=4.83</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2923,10 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>·塞尔塔:客胜(1.92)
+          <t>·塞尔塔:客胜(1.95)
 ·圣旺红星:客胜(1.65)
 ·南安普敦:客胜(1.50)
-·奥萨苏纳:客胜(1.52)</t>
+·奥萨苏纳:客胜(1.50)</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>1.92×1.65×1.50×1.52=7.22</t>
+          <t>1.95×1.65×1.50×1.50=7.24</t>
         </is>
       </c>
     </row>
@@ -3123,8 +3123,8 @@
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：韩职
-竞彩SP：6.25 / 3.85 / 1.41
-让球SP(真实)：2.49/2.80/2.70
+欧赔(spf)：6.25 / 3.85 / 1.41
+竞彩SP: 2.49/2.80/2.70
 差值分析：P主=31% P平=29% P客=40%
 推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让-1 走水=让平 </t>
@@ -3143,8 +3143,8 @@
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：韩职
-竞彩SP：2.88 / 3.30 / 2.09
-让球SP(真实)：7.80/4.20/1.31
+欧赔(spf)：2.88 / 3.3 / 2.09
+竞彩SP: 7.80/4.20/1.31
 差值分析：P主=36% P平=30% P客=34%
 推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
 让球:让+1 走水=让平 </t>
@@ -3163,8 +3163,8 @@
         <is>
           <t xml:space="preserve">时间：01:00
 联赛：西甲
-竞彩SP：3.10 / 3.50 / 1.92
-让球SP(真实)：1.67/3.60/3.95
+欧赔(spf)：3.1 / 3.4 / 1.95
+竞彩SP: 1.67/3.60/3.95
 差值分析：P主=34% P平=28% P客=38%
 推荐：客胜 信心3/10 比分1-2(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:平负
 让球:让-1 走水=让平 </t>
@@ -3183,9 +3183,9 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：沙特职业联赛
-竞彩SP：3.76 / 4.00 / 1.63
-让球SP(真实)：1.98/3.70/2.82
-差值分析：P主=33% P平=28% P客=39%
+欧赔(spf)：3.87 / 4.0 / 1.61
+竞彩SP: 2.00/3.64/2.82
+差值分析：P主=33% P平=28% P客=40%
 推荐：客胜 信心1/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让-1 走水=让平 </t>
         </is>
@@ -3203,8 +3203,8 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：西甲
-竞彩SP：2.50 / 3.40 / 2.30
-让球SP(真实)：1.46/4.10/5.00
+欧赔(spf)：2.5 / 3.3 / 2.35
+竞彩SP: 1.46/4.10/5.00
 差值分析：P主=38% P平=28% P客=34%
 推荐：主胜 信心2/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
@@ -3223,8 +3223,8 @@
         <is>
           <t xml:space="preserve">时间：02:30
 联赛：法甲
-竞彩SP：4.15 / 3.55 / 1.65
-让球SP(真实)：1.95/3.15/3.35
+欧赔(spf)：4.15 / 3.55 / 1.65
+竞彩SP: 1.95/3.15/3.35
 差值分析：P主=32% P平=29% P客=39%
 推荐：客胜 信心3/10 比分0-1(泊松) 半全场负负 大小球小2.5(40%) 备选半全场:平负
 让球:让-1 走水=让平 </t>
@@ -3243,8 +3243,8 @@
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：英冠
-竞彩SP：4.60 / 4.08 / 1.50
-让球SP(真实)：2.20/3.22/2.75
+欧赔(spf)：4.6 / 4.08 / 1.5
+竞彩SP: 2.20/3.22/2.75
 差值分析：P主=35% P平=27% P客=38%
 推荐：客胜 信心3/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
 让球:让-1 穿盘=让胜 </t>
@@ -3263,8 +3263,8 @@
         <is>
           <t xml:space="preserve">时间：03:30
 联赛：西甲
-竞彩SP：4.65 / 3.90 / 1.52
-让球SP(真实)：2.18/3.30/2.72
+欧赔(spf)：4.85 / 3.9 / 1.5
+竞彩SP: 2.25/3.25/2.65
 差值分析：P主=29% P平=26% P客=45%
 推荐：客胜 信心3/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
 让球:让-1 穿盘=让胜 </t>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>·塞尔塔:客胜(1.92)
+          <t>·塞尔塔:客胜(1.95)
 ·圣旺红星:客胜(1.65)</t>
         </is>
       </c>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>3.17倍</t>
+          <t>3.22倍</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>·塞尔塔:客胜(1.92)
+          <t>·塞尔塔:客胜(1.95)
 ·圣旺红星:客胜(1.65)
 ·南安普敦:客胜(1.50)</t>
         </is>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>4.75倍</t>
+          <t>4.83倍</t>
         </is>
       </c>
     </row>
@@ -3458,10 +3458,10 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>·塞尔塔:客胜(1.92)
+          <t>·塞尔塔:客胜(1.95)
 ·圣旺红星:客胜(1.65)
 ·南安普敦:客胜(1.50)
-·奥萨苏纳:客胜(1.52)</t>
+·奥萨苏纳:客胜(1.50)</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>7.22倍</t>
+          <t>7.24倍</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>79.00</t>
+          <t>80.00</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>79元</t>
+          <t>80元</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>79.00倍</t>
+          <t>80.00倍</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>594.00</t>
+          <t>603.00</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>594元</t>
+          <t>603元</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>594.00倍</t>
+          <t>603.00倍</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>4.75倍</t>
+          <t>4.83倍</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>7.24</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>7.22倍</t>
+          <t>7.24倍</t>
         </is>
       </c>
     </row>

--- a/Aii竞彩推荐_2026-05-12.xlsx
+++ b/Aii竞彩推荐_2026-05-12.xlsx
@@ -593,7 +593,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 16:42</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 17:15</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP6.85/3.95/1.37 让球-1</t>
+          <t>SP7.10/3.95/1.36 让球-1</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>SP3.04/3.30/2.01 让球+1</t>
+          <t>SP2.92/3.45/2.01 让球+1</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP3.15/3.34/1.95 让球-1</t>
+          <t>SP3.29/3.20/1.95 让球-1</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>SP2.50/3.20/2.40 让球-1</t>
+          <t>SP2.56/3.10/2.40 让球-1</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>SP4.35/3.55/1.62 让球-1</t>
+          <t>SP4.48/3.55/1.60 让球-1</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 16:42</t>
+          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 17:15</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>6.85</v>
+        <v>7.1</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>3.95</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>2.01</v>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>3.15</v>
+        <v>3.29</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>1.95</v>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>2.4</v>
@@ -1347,13 +1347,13 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>4.35</v>
+        <v>4.48</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>3.55</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.64</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1602,22 +1602,22 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=35%P平=30%P客=35%|泊松比分0-1|半全场负负|大小球小2.5(42%)|让球+1=输盘/让胜|赔变主↑2% 平↑2% 客↓3%</t>
+          <t>贝叶斯P主=35%P平=30%P客=35%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球+1=走水/让平|赔变主↑2% 平↑2% 客↓3%</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=34%P平=28%P客=38%|泊松比分1-2|半全场负负|大小球大2.5(69%)|让球-1=走水/让平</t>
+          <t>贝叶斯P主=34%P平=28%P客=37%|泊松比分1-2|半全场负负|大小球大2.5(69%)|让球-1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=38%P平=29%P客=34%|泊松比分3-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜</t>
+          <t>贝叶斯P主=38%P平=29%P客=33%|泊松比分3-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       <c r="C79" s="6" t="inlineStr">
         <is>
           <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.62)</t>
+·圣旺红星:客胜(1.60)</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>1.95×1.62=3.16</t>
+          <t>1.95×1.60=3.12</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       <c r="C80" s="6" t="inlineStr">
         <is>
           <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.62)
+·圣旺红星:客胜(1.60)
 ·南安普敦:客胜(1.50)</t>
         </is>
       </c>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>1.95×1.62×1.50=4.74</t>
+          <t>1.95×1.60×1.50=4.68</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       <c r="C81" s="6" t="inlineStr">
         <is>
           <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.62)
+·圣旺红星:客胜(1.60)
 ·南安普敦:客胜(1.50)
 ·奥萨苏纳:客胜(1.47)</t>
         </is>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>1.95×1.62×1.50×1.47=6.97</t>
+          <t>1.95×1.60×1.50×1.47=6.88</t>
         </is>
       </c>
     </row>
@@ -3123,8 +3123,8 @@
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：韩职
-欧赔(spf)：6.85 / 3.95 / 1.37
-竞彩SP: 2.60/2.70/2.67
+欧赔(spf)：7.1 / 3.95 / 1.36
+竞彩SP: 2.65/2.65/2.67
 差值分析：P主=31% P平=29% P客=40%
 推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(40%) 备选半全场:平负
 让球:让-1 走水=让平 </t>
@@ -3143,11 +3143,11 @@
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：韩职
-欧赔(spf)：3.04 / 3.3 / 2.01
-竞彩SP: 8.10/4.45/1.28
+欧赔(spf)：2.92 / 3.45 / 2.01
+竞彩SP: 7.65/4.60/1.28
 差值分析：P主=35% P平=30% P客=35%
-推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(42%) 备选半全场:平负
-让球:让+1 输盘=让胜 </t>
+推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
+让球:让+1 走水=让平 </t>
         </is>
       </c>
     </row>
@@ -3163,9 +3163,9 @@
         <is>
           <t xml:space="preserve">时间：01:00
 联赛：西甲
-欧赔(spf)：3.15 / 3.34 / 1.95
+欧赔(spf)：3.29 / 3.2 / 1.95
 竞彩SP: 1.67/3.60/3.95
-差值分析：P主=34% P平=28% P客=38%
+差值分析：P主=34% P平=28% P客=37%
 推荐：客胜 信心3/10 比分1-2(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:平负
 让球:让-1 走水=让平 </t>
         </is>
@@ -3203,9 +3203,9 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：西甲
-欧赔(spf)：2.5 / 3.2 / 2.4
+欧赔(spf)：2.56 / 3.1 / 2.4
 竞彩SP: 1.44/4.10/5.25
-差值分析：P主=38% P平=29% P客=34%
+差值分析：P主=38% P平=29% P客=33%
 推荐：主胜 信心2/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
@@ -3223,8 +3223,8 @@
         <is>
           <t xml:space="preserve">时间：02:30
 联赛：法甲
-欧赔(spf)：4.35 / 3.55 / 1.62
-竞彩SP: 2.00/3.02/3.35
+欧赔(spf)：4.48 / 3.55 / 1.6
+竞彩SP: 2.03/2.96/3.35
 差值分析：P主=32% P平=29% P客=39%
 推荐：客胜 信心3/10 比分0-1(泊松) 半全场负负 大小球小2.5(40%) 备选半全场:平负
 让球:让-1 走水=让平 </t>
@@ -3264,7 +3264,7 @@
           <t xml:space="preserve">时间：03:30
 联赛：西甲
 欧赔(spf)：5.2 / 3.9 / 1.47
-竞彩SP: 2.31/3.25/2.57
+竞彩SP: 2.31/3.15/2.64
 差值分析：P主=28% P平=26% P客=46%
 推荐：客胜 信心3/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
 让球:让-1 穿盘=让胜 </t>
@@ -3376,7 +3376,7 @@
       <c r="C4" s="8" t="inlineStr">
         <is>
           <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.62)</t>
+·圣旺红星:客胜(1.60)</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>3.16倍</t>
+          <t>3.12倍</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       <c r="C5" s="8" t="inlineStr">
         <is>
           <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.62)
+·圣旺红星:客胜(1.60)
 ·南安普敦:客胜(1.50)</t>
         </is>
       </c>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>4.74倍</t>
+          <t>4.68倍</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3459,7 @@
       <c r="C6" s="8" t="inlineStr">
         <is>
           <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.62)
+·圣旺红星:客胜(1.60)
 ·南安普敦:客胜(1.50)
 ·奥萨苏纳:客胜(1.47)</t>
         </is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>6.97倍</t>
+          <t>6.88倍</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>79.00</t>
+          <t>78.00</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>79元</t>
+          <t>78元</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>79.00倍</t>
+          <t>78.00倍</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>592.00</t>
+          <t>585.00</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>592元</t>
+          <t>585元</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>592.00倍</t>
+          <t>585.00倍</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>4.74倍</t>
+          <t>4.68倍</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>6.97倍</t>
+          <t>6.88倍</t>
         </is>
       </c>
     </row>

--- a/Aii竞彩推荐_2026-05-12.xlsx
+++ b/Aii竞彩推荐_2026-05-12.xlsx
@@ -593,7 +593,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 17:15</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 17:28</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP7.10/3.95/1.36 让球-1</t>
+          <t>SP8.50/4.25/1.29 让球-1</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>SP2.92/3.45/2.01 让球+1</t>
+          <t>SP2.82/3.45/2.06 让球+1</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 17:15</t>
+          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 17:28</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>3.95</v>
+        <v>4.25</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
@@ -1132,17 +1132,17 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
           <t>2.65</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
-      </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.42</t>
         </is>
       </c>
     </row>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>3.45</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.30</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=31%P平=29%P客=40%|泊松比分0-1|半全场负负|大小球小2.5(40%)|让球-1=走水/让平</t>
+          <t>贝叶斯P主=31%P平=28%P客=41%|泊松比分0-1|半全场负负|大小球小2.5(40%)|让球-1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=35%P平=30%P客=35%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球+1=走水/让平|赔变主↑2% 平↑2% 客↓3%</t>
+          <t>贝叶斯P主=36%P平=30%P客=34%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球+1=走水/让平|赔变主↑2% 平↑2% 客↓3%</t>
         </is>
       </c>
     </row>
@@ -3123,9 +3123,9 @@
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：韩职
-欧赔(spf)：7.1 / 3.95 / 1.36
-竞彩SP: 2.65/2.65/2.67
-差值分析：P主=31% P平=29% P客=40%
+欧赔(spf)：8.5 / 4.25 / 1.29
+竞彩SP: 2.95/2.65/2.42
+差值分析：P主=31% P平=28% P客=41%
 推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(40%) 备选半全场:平负
 让球:让-1 走水=让平 </t>
         </is>
@@ -3143,9 +3143,9 @@
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：韩职
-欧赔(spf)：2.92 / 3.45 / 2.01
-竞彩SP: 7.65/4.60/1.28
-差值分析：P主=35% P平=30% P客=35%
+欧赔(spf)：2.82 / 3.45 / 2.06
+竞彩SP: 7.00/4.60/1.30
+差值分析：P主=36% P平=30% P客=34%
 推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
 让球:让+1 走水=让平 </t>
         </is>

--- a/Aii竞彩推荐_2026-05-12.xlsx
+++ b/Aii竞彩推荐_2026-05-12.xlsx
@@ -593,7 +593,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 17:28</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 17:58</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP8.50/4.25/1.29 让球-1</t>
+          <t>SP6.25/3.85/1.41 让球-1</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>SP2.82/3.45/2.06 让球+1</t>
+          <t>SP7.00/4.60/1.30 让球+1</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP3.29/3.20/1.95 让球-1</t>
+          <t>SP1.67/3.60/3.95 让球-1</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>SP4.05/4.00/1.58 让球-1</t>
+          <t>SP2.06/3.45/2.82 让球-1</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>SP2.56/3.10/2.40 让球-1</t>
+          <t>SP1.44/4.10/5.25 让球-1</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>SP4.48/3.55/1.60 让球-1</t>
+          <t>SP2.03/2.96/3.35 让球-1</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>SP4.70/4.00/1.50 让球-1</t>
+          <t>SP2.20/3.15/2.80 让球-1</t>
         </is>
       </c>
     </row>
@@ -1037,14 +1037,14 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>SP5.20/3.90/1.47 让球-1</t>
+          <t>SP2.38/3.15/2.55 让球-1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 17:28</t>
+          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 17:58</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>8.5</v>
+        <v>6.25</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>4.25</v>
+        <v>3.85</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
@@ -1132,17 +1132,17 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1.26</t>
         </is>
       </c>
     </row>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2.82</v>
+        <v>7</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>2.06</v>
+        <v>1.3</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>3.29</v>
+        <v>1.67</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1.95</v>
+        <v>3.95</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
@@ -1224,17 +1224,17 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.97</t>
         </is>
       </c>
     </row>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>4.05</v>
+        <v>2.06</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1.58</v>
+        <v>2.82</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1270,17 +1270,17 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>1.58</t>
         </is>
       </c>
     </row>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>2.56</v>
+        <v>1.44</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>2.4</v>
+        <v>5.25</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
@@ -1347,13 +1347,13 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>4.48</v>
+        <v>2.03</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>3.55</v>
+        <v>2.96</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>1.6</v>
+        <v>3.35</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1362,17 +1362,17 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>1.60</t>
         </is>
       </c>
     </row>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.50</t>
         </is>
       </c>
     </row>
@@ -1439,13 +1439,13 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>5.2</v>
+        <v>2.38</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>1.47</v>
+        <v>2.55</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1454,17 +1454,17 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.43</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=31%P平=28%P客=41%|泊松比分0-1|半全场负负|大小球小2.5(40%)|让球-1=走水/让平</t>
+          <t>贝叶斯P主=31%P平=29%P客=40%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球-1=走水/让平</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1602,22 +1602,22 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>负负</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>平负</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=36%P平=30%P客=34%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球+1=走水/让平|赔变主↑2% 平↑2% 客↓3%</t>
+          <t>贝叶斯P主=31%P平=28%P客=41%|泊松比分0-1|半全场负负|大小球小2.5(40%)|让球+1=输盘/让胜|赔变主↑2% 平↑2% 客↓3%</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1654,22 +1654,22 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=34%P平=28%P客=37%|泊松比分1-2|半全场负负|大小球大2.5(69%)|让球-1=走水/让平</t>
+          <t>贝叶斯P主=44%P平=27%P客=29%|泊松比分2-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -1716,12 +1716,12 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=33%P平=28%P客=39%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球-1=走水/让平</t>
+          <t>贝叶斯P主=42%P平=28%P客=29%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>3/10</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=38%P平=29%P客=33%|泊松比分3-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜</t>
+          <t>贝叶斯P主=49%P平=26%P客=25%|泊松比分3-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=32%P平=29%P客=39%|泊松比分0-1|半全场负负|大小球小2.5(40%)|让球-1=走水/让平</t>
+          <t>贝叶斯P主=42%P平=30%P客=28%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
@@ -1852,17 +1852,17 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -1872,12 +1872,12 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=34%P平=27%P客=38%|泊松比分1-3|半全场负负|大小球大2.5(70%)|让球-1=穿盘/让胜</t>
+          <t>贝叶斯P主=44%P平=29%P客=27%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=28%P平=26%P客=46%|泊松比分1-3|半全场负负|大小球大2.5(70%)|让球-1=穿盘/让胜</t>
+          <t>贝叶斯P主=40%P平=27%P客=33%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
@@ -2845,13 +2845,13 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006</t>
+          <t>周二003+周二005</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.60)</t>
+          <t>·塞尔塔:主胜(1.67)
+·贝蒂斯:主胜(1.44)</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>1.95×1.60=3.12</t>
+          <t>1.67×1.44=2.40</t>
         </is>
       </c>
     </row>
@@ -2881,14 +2881,14 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006+周二007</t>
+          <t>周二003+周二005+周二006</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.60)
-·南安普敦:客胜(1.50)</t>
+          <t>·塞尔塔:主胜(1.67)
+·贝蒂斯:主胜(1.44)
+·圣旺红星:主胜(2.03)</t>
         </is>
       </c>
       <c r="D80" s="6" t="n">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>1.95×1.60×1.50=4.68</t>
+          <t>1.67×1.44×2.03=4.88</t>
         </is>
       </c>
     </row>
@@ -2918,15 +2918,15 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006+周二007+周二008</t>
+          <t>周二003+周二005+周二006+周二008</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.60)
-·南安普敦:客胜(1.50)
-·奥萨苏纳:客胜(1.47)</t>
+          <t>·塞尔塔:主胜(1.67)
+·贝蒂斯:主胜(1.44)
+·圣旺红星:主胜(2.03)
+·奥萨苏纳:主胜(2.38)</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>1.95×1.60×1.50×1.47=6.88</t>
+          <t>1.67×1.44×2.03×2.38=11.62</t>
         </is>
       </c>
     </row>
@@ -3123,31 +3123,31 @@
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：韩职
-欧赔(spf)：8.5 / 4.25 / 1.29
-竞彩SP: 2.95/2.65/2.42
+欧赔(spf)：6.25 / 3.85 / 1.41
+竞彩SP: 3.15/2.65/2.30
+差值分析：P主=31% P平=29% P客=40%
+推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
+让球:让-1 走水=让平 </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>⚽ 周二002 光州FC vs 首尔FC [韩职] 18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="130" customHeight="1">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：18:30
+联赛：韩职
+欧赔(spf)：7.0 / 4.6 / 1.3
+竞彩SP: 2.82/3.45/2.06
 差值分析：P主=31% P平=28% P客=41%
 推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(40%) 备选半全场:平负
-让球:让-1 走水=让平 </t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>⚽ 周二002 光州FC vs 首尔FC [韩职] 18:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="130" customHeight="1">
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：18:30
-联赛：韩职
-欧赔(spf)：2.82 / 3.45 / 2.06
-竞彩SP: 7.00/4.60/1.30
-差值分析：P主=36% P平=30% P客=34%
-推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
-让球:让+1 走水=让平 </t>
+让球:让+1 输盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -3163,11 +3163,11 @@
         <is>
           <t xml:space="preserve">时间：01:00
 联赛：西甲
-欧赔(spf)：3.29 / 3.2 / 1.95
-竞彩SP: 1.67/3.60/3.95
-差值分析：P主=34% P平=28% P客=37%
-推荐：客胜 信心3/10 比分1-2(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:平负
-让球:让-1 走水=让平 </t>
+欧赔(spf)：1.67 / 3.6 / 3.95
+竞彩SP: 3.35/3.10/1.97
+差值分析：P主=44% P平=27% P客=29%
+推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
+让球:让-1 输盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -3183,11 +3183,11 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：沙特职业联赛
-欧赔(spf)：4.05 / 4.0 / 1.58
-竞彩SP: 2.06/3.45/2.82
-差值分析：P主=33% P平=28% P客=39%
-推荐：客胜 信心1/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
-让球:让-1 走水=让平 </t>
+欧赔(spf)：2.06 / 3.45 / 2.82
+竞彩SP: 4.05/4.00/1.58
+差值分析：P主=42% P平=28% P客=29%
+推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
+让球:让-1 输盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -3203,10 +3203,10 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：西甲
-欧赔(spf)：2.56 / 3.1 / 2.4
-竞彩SP: 1.44/4.10/5.25
-差值分析：P主=38% P平=29% P客=33%
-推荐：主胜 信心2/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
+欧赔(spf)：1.44 / 4.1 / 5.25
+竞彩SP: 2.56/3.10/2.40
+差值分析：P主=49% P平=26% P客=25%
+推荐：主胜 信心3/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
       </c>
@@ -3223,11 +3223,11 @@
         <is>
           <t xml:space="preserve">时间：02:30
 联赛：法甲
-欧赔(spf)：4.48 / 3.55 / 1.6
-竞彩SP: 2.03/2.96/3.35
-差值分析：P主=32% P平=29% P客=39%
-推荐：客胜 信心3/10 比分0-1(泊松) 半全场负负 大小球小2.5(40%) 备选半全场:平负
-让球:让-1 走水=让平 </t>
+欧赔(spf)：2.03 / 2.96 / 3.35
+竞彩SP: 4.48/3.55/1.60
+差值分析：P主=42% P平=30% P客=28%
+推荐：主胜 信心3/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
+让球:让-1 输盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -3243,11 +3243,11 @@
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：英冠
-欧赔(spf)：4.7 / 4.0 / 1.5
-竞彩SP: 2.20/3.15/2.80
-差值分析：P主=34% P平=27% P客=38%
-推荐：客胜 信心3/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
-让球:让-1 穿盘=让胜 </t>
+欧赔(spf)：2.2 / 3.15 / 2.8
+竞彩SP: 4.70/4.00/1.50
+差值分析：P主=44% P平=29% P客=27%
+推荐：主胜 信心2/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
+让球:让-1 输盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -3263,11 +3263,11 @@
         <is>
           <t xml:space="preserve">时间：03:30
 联赛：西甲
-欧赔(spf)：5.2 / 3.9 / 1.47
-竞彩SP: 2.31/3.15/2.64
-差值分析：P主=28% P平=26% P客=46%
-推荐：客胜 信心3/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
-让球:让-1 穿盘=让胜 </t>
+欧赔(spf)：2.38 / 3.15 / 2.55
+竞彩SP: 5.55/4.00/1.43
+差值分析：P主=40% P平=27% P客=33%
+推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
+让球:让-1 输盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -3370,13 +3370,13 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>周二003+周二006</t>
+          <t>周二003+周二005</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.60)</t>
+          <t>·塞尔塔:主胜(1.67)
+·贝蒂斯:主胜(1.44)</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>6元</t>
+          <t>5元</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>3.12倍</t>
+          <t>2.40倍</t>
         </is>
       </c>
     </row>
@@ -3411,14 +3411,14 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>周二003+周二006+周二007</t>
+          <t>周二003+周二005+周二006</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.60)
-·南安普敦:客胜(1.50)</t>
+          <t>·塞尔塔:主胜(1.67)
+·贝蒂斯:主胜(1.44)
+·圣旺红星:主胜(2.03)</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>9元</t>
+          <t>10元</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>4.68倍</t>
+          <t>4.88倍</t>
         </is>
       </c>
     </row>
@@ -3453,15 +3453,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>周二003+周二006+周二007+周二008</t>
+          <t>周二003+周二005+周二006+周二008</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>·塞尔塔:客胜(1.95)
-·圣旺红星:客胜(1.60)
-·南安普敦:客胜(1.50)
-·奥萨苏纳:客胜(1.47)</t>
+          <t>·塞尔塔:主胜(1.67)
+·贝蒂斯:主胜(1.44)
+·圣旺红星:主胜(2.03)
+·奥萨苏纳:主胜(2.38)</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>14元</t>
+          <t>23元</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>6.88倍</t>
+          <t>11.62倍</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006</t>
+          <t>周二003+周二005</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>78.00</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>78元</t>
+          <t>60元</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>78.00倍</t>
+          <t>60.00倍</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006+周二007</t>
+          <t>周二003+周二005+周二006</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>585.00</t>
+          <t>610.00</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>585元</t>
+          <t>610元</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>585.00倍</t>
+          <t>610.00倍</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006+周二007</t>
+          <t>周二003+周二005+周二006</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>4.68倍</t>
+          <t>4.88倍</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006+周二007+周二008</t>
+          <t>周二003+周二005+周二006+周二008</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>7元</t>
+          <t>12元</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>6.88倍</t>
+          <t>11.62倍</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006</t>
+          <t>周二003+周二005</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>6元</t>
+          <t>5元</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>6.25倍</t>
+          <t>4.84倍</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006+周二007</t>
+          <t>周二003+周二005+周二006</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>16元</t>
+          <t>11元</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>15.62倍</t>
+          <t>10.65倍</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二006+周二007+周二008</t>
+          <t>周二003+周二005+周二006+周二008</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>39.06</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>39元</t>
+          <t>23元</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>39.06倍</t>
+          <t>23.43倍</t>
         </is>
       </c>
     </row>

--- a/Aii竞彩推荐_2026-05-12.xlsx
+++ b/Aii竞彩推荐_2026-05-12.xlsx
@@ -593,7 +593,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 17:58</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 18:41</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP6.25/3.85/1.41 让球-1</t>
+          <t>SP6.25/3.85/1.41 让球0</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>SP7.00/4.60/1.30 让球+1</t>
+          <t>SP7.00/4.50/1.40 让球+1</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP1.67/3.60/3.95 让球-1</t>
+          <t>SP1.75/3.40/4.45 让球-1</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>SP2.06/3.45/2.82 让球-1</t>
+          <t>SP2.22/3.35/2.60 让球-1</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>SP1.44/4.10/5.25 让球-1</t>
+          <t>SP1.66/4.15/5.00 让球-1</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>SP2.03/2.96/3.35 让球-1</t>
+          <t>SP1.83/3.80/3.45 让球-1</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>SP2.20/3.15/2.80 让球-1</t>
+          <t>SP2.36/3.75/2.74 让球-1</t>
         </is>
       </c>
     </row>
@@ -1037,14 +1037,14 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>SP2.38/3.15/2.55 让球-1</t>
+          <t>SP2.62/3.65/2.59 让球0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 17:58</t>
+          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 18:41</t>
         </is>
       </c>
     </row>
@@ -1127,22 +1127,22 @@
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>2.32</t>
         </is>
       </c>
     </row>
@@ -1166,10 +1166,10 @@
         <v>7</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>3.95</v>
+        <v>4.45</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
@@ -1224,17 +1224,17 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>4.30</t>
         </is>
       </c>
     </row>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1270,17 +1270,17 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.77</t>
         </is>
       </c>
     </row>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
@@ -1347,13 +1347,13 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>2.96</v>
+        <v>3.8</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
@@ -1439,32 +1439,32 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=31%P平=29%P客=40%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球-1=走水/让平</t>
+          <t>贝叶斯P主=31%P平=29%P客=40%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=31%P平=28%P客=41%|泊松比分0-1|半全场负负|大小球小2.5(40%)|让球+1=输盘/让胜|赔变主↑2% 平↑2% 客↓3%</t>
+          <t>贝叶斯P主=31%P平=28%P客=41%|泊松比分0-1|半全场负负|大小球小2.5(40%)|让球+1=输盘/让胜|赔变主↑149% 平↑42% 客↓40%</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=44%P平=27%P客=29%|泊松比分2-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜</t>
+          <t>贝叶斯P主=43%P平=28%P客=29%|泊松比分2-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜|赔变主↓46% 平↑3% 客↑106%</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=42%P平=28%P客=29%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让胜</t>
+          <t>贝叶斯P主=41%P平=29%P客=30%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让胜|赔变主↓45% 平↓14% 客↑73%</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=49%P平=26%P客=25%|泊松比分3-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜</t>
+          <t>贝叶斯P主=48%P平=26%P客=25%|泊松比分3-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜|赔变主↓42% 平↑21% 客↑128%</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=42%P平=30%P客=28%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让胜</t>
+          <t>贝叶斯P主=44%P平=28%P客=28%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让胜|赔变主↓51% 平↓17% 客↑103%</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=44%P平=29%P客=27%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让胜</t>
+          <t>贝叶斯P主=43%P平=28%P客=29%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让胜|赔变主↓52% 平↓23% 客↑87%</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>负负</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>平负</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=40%P平=27%P客=33%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让胜</t>
+          <t>贝叶斯P主=35%P平=26%P客=38%|泊松比分1-3|半全场负负|大小球大2.5(70%)|让球0=无让球/—|赔变主↓49% 平↓19% 客↑68%</t>
         </is>
       </c>
     </row>
@@ -2850,8 +2850,8 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>·塞尔塔:主胜(1.67)
-·贝蒂斯:主胜(1.44)</t>
+          <t>·塞尔塔:主胜(1.75)
+·贝蒂斯:主胜(1.66)</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>1.67×1.44=2.40</t>
+          <t>1.75×1.66=2.90</t>
         </is>
       </c>
     </row>
@@ -2886,9 +2886,9 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>·塞尔塔:主胜(1.67)
-·贝蒂斯:主胜(1.44)
-·圣旺红星:主胜(2.03)</t>
+          <t>·塞尔塔:主胜(1.75)
+·贝蒂斯:主胜(1.66)
+·圣旺红星:主胜(1.83)</t>
         </is>
       </c>
       <c r="D80" s="6" t="n">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>1.67×1.44×2.03=4.88</t>
+          <t>1.75×1.66×1.83=5.32</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2923,10 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>·塞尔塔:主胜(1.67)
-·贝蒂斯:主胜(1.44)
-·圣旺红星:主胜(2.03)
-·奥萨苏纳:主胜(2.38)</t>
+          <t>·塞尔塔:主胜(1.75)
+·贝蒂斯:主胜(1.66)
+·圣旺红星:主胜(1.83)
+·奥萨苏纳:客胜(2.59)</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>13.77</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>1.67×1.44×2.03×2.38=11.62</t>
+          <t>1.75×1.66×1.83×2.59=13.77</t>
         </is>
       </c>
     </row>
@@ -3124,10 +3124,10 @@
           <t xml:space="preserve">时间：18:30
 联赛：韩职
 欧赔(spf)：6.25 / 3.85 / 1.41
-竞彩SP: 3.15/2.65/2.30
+竞彩SP: 2.49/2.80/2.70
 差值分析：P主=31% P平=29% P客=40%
 推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
-让球:让-1 走水=让平 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：韩职
-欧赔(spf)：7.0 / 4.6 / 1.3
+欧赔(spf)：7.0 / 4.5 / 1.4
 竞彩SP: 2.82/3.45/2.06
 差值分析：P主=31% P平=28% P客=41%
 推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(40%) 备选半全场:平负
@@ -3163,9 +3163,9 @@
         <is>
           <t xml:space="preserve">时间：01:00
 联赛：西甲
-欧赔(spf)：1.67 / 3.6 / 3.95
-竞彩SP: 3.35/3.10/1.97
-差值分析：P主=44% P平=27% P客=29%
+欧赔(spf)：1.75 / 3.4 / 4.45
+竞彩SP: 1.67/3.50/3.95
+差值分析：P主=43% P平=28% P客=29%
 推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
@@ -3183,9 +3183,9 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：沙特职业联赛
-欧赔(spf)：2.06 / 3.45 / 2.82
-竞彩SP: 4.05/4.00/1.58
-差值分析：P主=42% P平=28% P客=29%
+欧赔(spf)：2.22 / 3.35 / 2.6
+竞彩SP: 1.98/3.70/2.82
+差值分析：P主=41% P平=29% P客=30%
 推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
@@ -3203,9 +3203,9 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：西甲
-欧赔(spf)：1.44 / 4.1 / 5.25
-竞彩SP: 2.56/3.10/2.40
-差值分析：P主=49% P平=26% P客=25%
+欧赔(spf)：1.66 / 4.15 / 5.0
+竞彩SP: 1.46/4.10/5.00
+差值分析：P主=48% P平=26% P客=25%
 推荐：主胜 信心3/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
@@ -3223,9 +3223,9 @@
         <is>
           <t xml:space="preserve">时间：02:30
 联赛：法甲
-欧赔(spf)：2.03 / 2.96 / 3.35
-竞彩SP: 4.48/3.55/1.60
-差值分析：P主=42% P平=30% P客=28%
+欧赔(spf)：1.83 / 3.8 / 3.45
+竞彩SP: 1.95/3.15/3.35
+差值分析：P主=44% P平=28% P客=28%
 推荐：主胜 信心3/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
@@ -3243,9 +3243,9 @@
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：英冠
-欧赔(spf)：2.2 / 3.15 / 2.8
-竞彩SP: 4.70/4.00/1.50
-差值分析：P主=44% P平=29% P客=27%
+欧赔(spf)：2.36 / 3.75 / 2.74
+竞彩SP: 2.20/3.15/2.80
+差值分析：P主=43% P平=28% P客=29%
 推荐：主胜 信心2/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
@@ -3263,11 +3263,11 @@
         <is>
           <t xml:space="preserve">时间：03:30
 联赛：西甲
-欧赔(spf)：2.38 / 3.15 / 2.55
-竞彩SP: 5.55/4.00/1.43
-差值分析：P主=40% P平=27% P客=33%
-推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
-让球:让-1 输盘=让胜 </t>
+欧赔(spf)：2.62 / 3.65 / 2.59
+竞彩SP: 2.18/3.30/2.72
+差值分析：P主=35% P平=26% P客=38%
+推荐：客胜 信心3/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
@@ -3375,8 +3375,8 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>·塞尔塔:主胜(1.67)
-·贝蒂斯:主胜(1.44)</t>
+          <t>·塞尔塔:主胜(1.75)
+·贝蒂斯:主胜(1.66)</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>5元</t>
+          <t>6元</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>2.40倍</t>
+          <t>2.90倍</t>
         </is>
       </c>
     </row>
@@ -3416,9 +3416,9 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>·塞尔塔:主胜(1.67)
-·贝蒂斯:主胜(1.44)
-·圣旺红星:主胜(2.03)</t>
+          <t>·塞尔塔:主胜(1.75)
+·贝蒂斯:主胜(1.66)
+·圣旺红星:主胜(1.83)</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>10元</t>
+          <t>11元</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>4.88倍</t>
+          <t>5.32倍</t>
         </is>
       </c>
     </row>
@@ -3458,10 +3458,10 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>·塞尔塔:主胜(1.67)
-·贝蒂斯:主胜(1.44)
-·圣旺红星:主胜(2.03)
-·奥萨苏纳:主胜(2.38)</t>
+          <t>·塞尔塔:主胜(1.75)
+·贝蒂斯:主胜(1.66)
+·圣旺红星:主胜(1.83)
+·奥萨苏纳:客胜(2.59)</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>13.77</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>23元</t>
+          <t>28元</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>11.62倍</t>
+          <t>13.77倍</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>73.00</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>60元</t>
+          <t>73元</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>60.00倍</t>
+          <t>73.00倍</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>610.00</t>
+          <t>665.00</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>610元</t>
+          <t>665元</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>610.00倍</t>
+          <t>665.00倍</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>4.88倍</t>
+          <t>5.32倍</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>13.77</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>12元</t>
+          <t>14元</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>11.62倍</t>
+          <t>13.77倍</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>26.62</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>23元</t>
+          <t>27元</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>23.43倍</t>
+          <t>26.62倍</t>
         </is>
       </c>
     </row>

--- a/Aii竞彩推荐_2026-05-12.xlsx
+++ b/Aii竞彩推荐_2026-05-12.xlsx
@@ -593,7 +593,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 18:41</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 19:02</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP6.25/3.85/1.41 让球0</t>
+          <t>SP2.59/3.15/2.66 让球0</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>SP7.00/4.50/1.40 让球+1</t>
+          <t>SP7.20/4.45/1.39 让球+1</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP1.75/3.40/4.45 让球-1</t>
+          <t>SP1.75/4.10/4.45 让球-1</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>SP2.22/3.35/2.60 让球-1</t>
+          <t>SP2.22/3.75/2.60 让球-1</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>SP2.36/3.75/2.74 让球-1</t>
+          <t>SP2.36/3.75/2.77 让球-1</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 18:41</t>
+          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 19:02</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>6.25</v>
+        <v>2.59</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1.41</v>
+        <v>2.66</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>1.75</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>4.45</v>
@@ -1224,17 +1224,17 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>1.92</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
         <v>2.22</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>2.6</v>
@@ -1270,17 +1270,17 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>1.63</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
         <v>3.75</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1550,22 +1550,22 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=31%P平=29%P客=40%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=39%P平=30%P客=30%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=43%P平=28%P客=29%|泊松比分2-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜|赔变主↓46% 平↑3% 客↑106%</t>
+          <t>贝叶斯P主=44%P平=27%P客=29%|泊松比分2-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜|赔变主↓46% 平↑3% 客↑106%</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=41%P平=29%P客=30%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让胜|赔变主↓45% 平↓14% 客↑73%</t>
+          <t>贝叶斯P主=41%P平=28%P客=31%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让胜|赔变主↓45% 平↓14% 客↑73%</t>
         </is>
       </c>
     </row>
@@ -3029,12 +3029,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>周二001</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>0场平局概率30%+</t>
+          <t>1场平局概率30%+</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -3123,10 +3123,10 @@
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：韩职
-欧赔(spf)：6.25 / 3.85 / 1.41
+欧赔(spf)：2.59 / 3.15 / 2.66
 竞彩SP: 2.49/2.80/2.70
-差值分析：P主=31% P平=29% P客=40%
-推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
+差值分析：P主=39% P平=30% P客=30%
+推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
 让球:让0 无让球=— </t>
         </is>
       </c>
@@ -3143,8 +3143,8 @@
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：韩职
-欧赔(spf)：7.0 / 4.5 / 1.4
-竞彩SP: 2.82/3.45/2.06
+欧赔(spf)：7.2 / 4.45 / 1.39
+竞彩SP: 7.70/4.15/1.32
 差值分析：P主=31% P平=28% P客=41%
 推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(40%) 备选半全场:平负
 让球:让+1 输盘=让胜 </t>
@@ -3163,9 +3163,9 @@
         <is>
           <t xml:space="preserve">时间：01:00
 联赛：西甲
-欧赔(spf)：1.75 / 3.4 / 4.45
-竞彩SP: 1.67/3.50/3.95
-差值分析：P主=43% P平=28% P客=29%
+欧赔(spf)：1.75 / 4.1 / 4.45
+竞彩SP: 1.67/3.60/3.95
+差值分析：P主=44% P平=27% P客=29%
 推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
@@ -3183,9 +3183,9 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：沙特职业联赛
-欧赔(spf)：2.22 / 3.35 / 2.6
+欧赔(spf)：2.22 / 3.75 / 2.6
 竞彩SP: 1.98/3.70/2.82
-差值分析：P主=41% P平=29% P客=30%
+差值分析：P主=41% P平=28% P客=31%
 推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
@@ -3243,8 +3243,8 @@
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：英冠
-欧赔(spf)：2.36 / 3.75 / 2.74
-竞彩SP: 2.20/3.15/2.80
+欧赔(spf)：2.36 / 3.75 / 2.77
+竞彩SP: 2.20/3.22/2.75
 差值分析：P主=43% P平=28% P客=29%
 推荐：主胜 信心2/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>

--- a/Aii竞彩推荐_2026-05-12.xlsx
+++ b/Aii竞彩推荐_2026-05-12.xlsx
@@ -593,7 +593,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 19:02</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 21:01</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP2.59/3.15/2.66 让球0</t>
+          <t>SP3.20/2.60/2.32 让球-1</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>SP7.20/4.45/1.39 让球+1</t>
+          <t>SP7.00/4.60/1.30 让球+1</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP1.75/4.10/4.45 让球-1</t>
+          <t>SP1.74/3.52/3.70 让球-1</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>SP2.22/3.75/2.60 让球-1</t>
+          <t>SP2.18/3.14/2.84 让球-1</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>SP1.66/4.15/5.00 让球-1</t>
+          <t>SP1.44/4.10/5.25 让球-1</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>SP1.83/3.80/3.45 让球-1</t>
+          <t>SP2.12/2.80/3.34 让球-1</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>SP2.36/3.75/2.77 让球-1</t>
+          <t>SP2.17/3.15/2.85 让球-1</t>
         </is>
       </c>
     </row>
@@ -1037,14 +1037,14 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>SP2.62/3.65/2.59 让球0</t>
+          <t>SP2.40/3.08/2.58 让球-1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 19:02</t>
+          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 21:01</t>
         </is>
       </c>
     </row>
@@ -1117,32 +1117,32 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>2.66</v>
+        <v>2.32</v>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>9.25</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.25</t>
         </is>
       </c>
     </row>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>4.1</v>
+        <v>3.52</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>4.45</v>
+        <v>3.7</v>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
@@ -1224,17 +1224,17 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.86</t>
         </is>
       </c>
     </row>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1270,17 +1270,17 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.51</t>
         </is>
       </c>
     </row>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
@@ -1347,13 +1347,13 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.56</t>
         </is>
       </c>
     </row>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.51</t>
         </is>
       </c>
     </row>
@@ -1439,32 +1439,32 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>3.65</v>
+        <v>3.08</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.43</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=39%P平=30%P客=30%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球0=无让球/—</t>
+          <t>贝叶斯P主=36%P平=32%P客=33%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球-1=输盘/让胜|赔变主↓59% 平↓18% 客↑89%</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=31%P平=28%P客=41%|泊松比分0-1|半全场负负|大小球小2.5(40%)|让球+1=输盘/让胜|赔变主↑149% 平↑42% 客↓40%</t>
+          <t>贝叶斯P主=31%P平=28%P客=41%|泊松比分0-1|半全场负负|大小球小2.5(40%)|让球+1=输盘/让胜|赔变主↑156% 平↑37% 客↓35%</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=44%P平=27%P客=29%|泊松比分2-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜|赔变主↓46% 平↑3% 客↑106%</t>
+          <t>贝叶斯P主=43%P平=28%P客=30%|泊松比分2-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜|赔变主↓44% 平↑17% 客↑132%</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=41%P平=28%P客=31%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让胜|赔变主↓45% 平↓14% 客↑73%</t>
+          <t>贝叶斯P主=42%P平=29%P客=29%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让胜|赔变主↓41% 平↓6% 客↑60%</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=48%P平=26%P客=25%|泊松比分3-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜|赔变主↓42% 平↑21% 客↑128%</t>
+          <t>贝叶斯P主=49%P平=26%P客=25%|泊松比分3-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜|赔变主↓34% 平↑22% 客↑117%</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=44%P平=28%P客=28%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让胜|赔变主↓51% 平↓17% 客↑103%</t>
+          <t>贝叶斯P主=42%P平=30%P客=28%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球-1=输盘/让胜|赔变主↓56% 平↑7% 客↑109%</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=43%P平=28%P客=29%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让胜|赔变主↓52% 平↓23% 客↑87%</t>
+          <t>贝叶斯P主=44%P平=29%P客=27%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让胜|赔变主↓49% 平↓8% 客↑85%</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=35%P平=26%P客=38%|泊松比分1-3|半全场负负|大小球大2.5(70%)|让球0=无让球/—|赔变主↓49% 平↓19% 客↑68%</t>
+          <t>贝叶斯P主=40%P平=27%P客=33%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让胜|赔变主↓44% 平↓6% 客↑70%</t>
         </is>
       </c>
     </row>
@@ -2850,8 +2850,8 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>·塞尔塔:主胜(1.75)
-·贝蒂斯:主胜(1.66)</t>
+          <t>·塞尔塔:主胜(1.74)
+·贝蒂斯:主胜(1.44)</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>1.75×1.66=2.90</t>
+          <t>1.74×1.44=2.51</t>
         </is>
       </c>
     </row>
@@ -2886,9 +2886,9 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>·塞尔塔:主胜(1.75)
-·贝蒂斯:主胜(1.66)
-·圣旺红星:主胜(1.83)</t>
+          <t>·塞尔塔:主胜(1.74)
+·贝蒂斯:主胜(1.44)
+·圣旺红星:主胜(2.12)</t>
         </is>
       </c>
       <c r="D80" s="6" t="n">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>1.75×1.66×1.83=5.32</t>
+          <t>1.74×1.44×2.12=5.31</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2923,10 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>·塞尔塔:主胜(1.75)
-·贝蒂斯:主胜(1.66)
-·圣旺红星:主胜(1.83)
-·奥萨苏纳:客胜(2.59)</t>
+          <t>·塞尔塔:主胜(1.74)
+·贝蒂斯:主胜(1.44)
+·圣旺红星:主胜(2.12)
+·奥萨苏纳:主胜(2.40)</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>13.77</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>1.75×1.66×1.83×2.59=13.77</t>
+          <t>1.74×1.44×2.12×2.40=12.75</t>
         </is>
       </c>
     </row>
@@ -3029,12 +3029,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>周二001</t>
+          <t>周二001/周二006</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>1场平局概率30%+</t>
+          <t>2场平局概率30%+</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -3123,11 +3123,11 @@
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：韩职
-欧赔(spf)：2.59 / 3.15 / 2.66
-竞彩SP: 2.49/2.80/2.70
-差值分析：P主=39% P平=30% P客=30%
-推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
-让球:让0 无让球=— </t>
+欧赔(spf)：3.2 / 2.6 / 2.32
+竞彩SP: 9.25/4.55/1.25
+差值分析：P主=36% P平=32% P客=33%
+推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
+让球:让-1 输盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -3143,8 +3143,8 @@
         <is>
           <t xml:space="preserve">时间：18:30
 联赛：韩职
-欧赔(spf)：7.2 / 4.45 / 1.39
-竞彩SP: 7.70/4.15/1.32
+欧赔(spf)：7.0 / 4.6 / 1.3
+竞彩SP: 2.82/3.45/2.06
 差值分析：P主=31% P平=28% P客=41%
 推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(40%) 备选半全场:平负
 让球:让+1 输盘=让胜 </t>
@@ -3163,9 +3163,9 @@
         <is>
           <t xml:space="preserve">时间：01:00
 联赛：西甲
-欧赔(spf)：1.75 / 4.1 / 4.45
-竞彩SP: 1.67/3.60/3.95
-差值分析：P主=44% P平=27% P客=29%
+欧赔(spf)：1.74 / 3.52 / 3.7
+竞彩SP: 3.60/3.18/1.86
+差值分析：P主=43% P平=28% P客=30%
 推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
@@ -3183,9 +3183,9 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：沙特职业联赛
-欧赔(spf)：2.22 / 3.75 / 2.6
-竞彩SP: 1.98/3.70/2.82
-差值分析：P主=41% P平=28% P客=31%
+欧赔(spf)：2.18 / 3.14 / 2.84
+竞彩SP: 4.40/4.18/1.51
+差值分析：P主=42% P平=29% P客=29%
 推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
@@ -3203,9 +3203,9 @@
         <is>
           <t xml:space="preserve">时间：02:00
 联赛：西甲
-欧赔(spf)：1.66 / 4.15 / 5.0
-竞彩SP: 1.46/4.10/5.00
-差值分析：P主=48% P平=26% P客=25%
+欧赔(spf)：1.44 / 4.1 / 5.25
+竞彩SP: 2.60/3.05/2.40
+差值分析：P主=49% P平=26% P客=25%
 推荐：主胜 信心3/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
@@ -3223,10 +3223,10 @@
         <is>
           <t xml:space="preserve">时间：02:30
 联赛：法甲
-欧赔(spf)：1.83 / 3.8 / 3.45
-竞彩SP: 1.95/3.15/3.35
-差值分析：P主=44% P平=28% P客=28%
-推荐：主胜 信心3/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
+欧赔(spf)：2.12 / 2.8 / 3.34
+竞彩SP: 4.85/3.55/1.56
+差值分析：P主=42% P平=30% P客=28%
+推荐：主胜 信心3/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
       </c>
@@ -3243,9 +3243,9 @@
         <is>
           <t xml:space="preserve">时间：03:00
 联赛：英冠
-欧赔(spf)：2.36 / 3.75 / 2.77
-竞彩SP: 2.20/3.22/2.75
-差值分析：P主=43% P平=28% P客=29%
+欧赔(spf)：2.17 / 3.15 / 2.85
+竞彩SP: 4.70/3.94/1.51
+差值分析：P主=44% P平=29% P客=27%
 推荐：主胜 信心2/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
@@ -3263,11 +3263,11 @@
         <is>
           <t xml:space="preserve">时间：03:30
 联赛：西甲
-欧赔(spf)：2.62 / 3.65 / 2.59
-竞彩SP: 2.18/3.30/2.72
-差值分析：P主=35% P平=26% P客=38%
-推荐：客胜 信心3/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
-让球:让0 无让球=— </t>
+欧赔(spf)：2.4 / 3.08 / 2.58
+竞彩SP: 5.55/4.00/1.43
+差值分析：P主=40% P平=27% P客=33%
+推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
+让球:让-1 输盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -3375,8 +3375,8 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>·塞尔塔:主胜(1.75)
-·贝蒂斯:主胜(1.66)</t>
+          <t>·塞尔塔:主胜(1.74)
+·贝蒂斯:主胜(1.44)</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>6元</t>
+          <t>5元</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>2.90倍</t>
+          <t>2.51倍</t>
         </is>
       </c>
     </row>
@@ -3416,9 +3416,9 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>·塞尔塔:主胜(1.75)
-·贝蒂斯:主胜(1.66)
-·圣旺红星:主胜(1.83)</t>
+          <t>·塞尔塔:主胜(1.74)
+·贝蒂斯:主胜(1.44)
+·圣旺红星:主胜(2.12)</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>5.32倍</t>
+          <t>5.31倍</t>
         </is>
       </c>
     </row>
@@ -3458,10 +3458,10 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>·塞尔塔:主胜(1.75)
-·贝蒂斯:主胜(1.66)
-·圣旺红星:主胜(1.83)
-·奥萨苏纳:客胜(2.59)</t>
+          <t>·塞尔塔:主胜(1.74)
+·贝蒂斯:主胜(1.44)
+·圣旺红星:主胜(2.12)
+·奥萨苏纳:主胜(2.40)</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>13.77</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>28元</t>
+          <t>26元</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>13.77倍</t>
+          <t>12.75倍</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>73.00</t>
+          <t>63.00</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>73元</t>
+          <t>63元</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>73.00倍</t>
+          <t>63.00倍</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>665.00</t>
+          <t>664.00</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>665元</t>
+          <t>664元</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>665.00倍</t>
+          <t>664.00倍</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>5.32倍</t>
+          <t>5.31倍</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>13.77</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>14元</t>
+          <t>13元</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>13.77倍</t>
+          <t>12.75倍</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>26.62</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>27元</t>
+          <t>23元</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>26.62倍</t>
+          <t>23.43倍</t>
         </is>
       </c>
     </row>

--- a/Aii竞彩推荐_2026-05-12.xlsx
+++ b/Aii竞彩推荐_2026-05-12.xlsx
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -586,14 +586,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🌍 2026-05-12 周二8场竞彩推荐·含14场(期号查sporttery)</t>
+          <t>🌍 2026-05-12 周二18场竞彩推荐·含14场(期号查sporttery)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 21:01</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 21:19</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2025-26赛季末段，保级+欧战争夺激烈。8场竞彩+14场(需查lottery.gov.cn官方奖期)。</t>
+          <t>2025-26赛季末段，保级+欧战争夺激烈。18场竞彩+14场(需查lottery.gov.cn官方奖期)。</t>
         </is>
       </c>
     </row>
@@ -668,27 +668,27 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>周二001</t>
+          <t>周二003</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>05-13 01:00</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>仁川联</t>
+          <t>塞尔塔</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>浦项制铁</t>
+          <t>莱万特</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>韩职</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -708,34 +708,34 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP3.20/2.60/2.32 让球-1</t>
+          <t>SP1.85/3.75/4.00 让球-1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>周二002</t>
+          <t>周二004</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>05-13 02:00</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>光州FC</t>
+          <t>利雅得胜利</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>首尔FC</t>
+          <t>利雅得新月</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>韩职</t>
+          <t>沙特联</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -755,29 +755,29 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>SP7.00/4.60/1.30 让球+1</t>
+          <t>SP2.20/3.40/2.88 让球-1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>周二003</t>
+          <t>周二005</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>05-13 02:00</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>塞尔塔</t>
+          <t>贝蒂斯</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>莱万特</t>
+          <t>埃尔切</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -802,34 +802,34 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP1.74/3.52/3.70 让球-1</t>
+          <t>SP1.57/4.33/5.25 让球-2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>周二004</t>
+          <t>周二006</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>05-13 02:30</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>利雅得胜利</t>
+          <t>红星</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>利雅得新月</t>
+          <t>罗德兹</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>沙特职业联赛</t>
+          <t>法乙</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -849,34 +849,34 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>SP2.18/3.14/2.84 让球-1</t>
+          <t>SP2.25/3.25/3.20 让球-1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>周二005</t>
+          <t>周二007</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>05-13 03:00</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>贝蒂斯</t>
+          <t>南安普顿</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>埃尔切</t>
+          <t>米德尔斯堡</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>英冠</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -896,34 +896,34 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>SP1.44/4.10/5.25 让球-1</t>
+          <t>SP2.45/3.40/2.80 让球-1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>周二006</t>
+          <t>周二008</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>05-13 03:30</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>圣旺红星</t>
+          <t>奥萨苏纳</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>罗德兹</t>
+          <t>马竞</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>法甲</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -943,34 +943,34 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>SP2.12/2.80/3.34 让球-1</t>
+          <t>SP2.60/3.50/2.60 让球-1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>周二007</t>
+          <t>周三001</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>05-13 18:00</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>南安普敦</t>
+          <t>神户胜利船</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>米堡</t>
+          <t>京都不死鸟</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>英冠</t>
+          <t>日职</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -990,2076 +990,3605 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>SP2.17/3.15/2.85 让球-1</t>
+          <t>SP1.75/3.60/4.75 让球-1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>周二008</t>
+          <t>周三002</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>05-13 18:30</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>奥萨苏纳</t>
+          <t>富川FC</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>马竞</t>
+          <t>全北现代</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
+          <t>K1联赛</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>常规赛</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>SP4.33/3.40/1.75 让球+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>周三003</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>05-14 01:00</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>比利亚雷亚尔</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>塞维利亚</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
           <t>西甲</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>常规赛</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>SP2.40/3.08/2.58 让球-1</t>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>SP2.05/3.30/3.75 让球-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>周三004</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>05-14 01:00</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>西班牙人</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>毕尔巴鄂</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>常规赛</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>SP2.63/3.30/2.70 让球+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>周三005</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>05-14 01:00</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>布雷斯特</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>斯特拉斯堡</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>法甲</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>常规赛</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>SP2.63/3.60/2.50 让球+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>周三006</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>05-14 03:00</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>曼城</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>水晶宫</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>英超</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>常规赛</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>SP1.20/7.50/12.00 让球-2</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 21:01</t>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>周三007</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>05-14 03:00</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>拉齐奥</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>国米</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>意杯</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>常规赛</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>SP5.25/3.90/1.62 让球+1</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>场次</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>联赛</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>主vs客</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>欧赔胜</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>欧赔平</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>欧赔负</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>让球数</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>竞彩SP胜</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>竞彩SP平</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>竞彩SP负</t>
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>周三008</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>05-14 03:00</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>朗斯</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>巴黎圣日耳曼</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>法甲</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>常规赛</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>SP3.40/4.00/1.95 让球+1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>周二001</t>
+          <t>周三009</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>韩职</t>
+          <t>05-14 03:30</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>仁川联vs浦项制铁</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>2.32</v>
+          <t>阿拉维斯</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>巴萨</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>常规赛</t>
+        </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>9.25</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>4.55</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>1.25</t>
+          <t>SP3.10/3.75/2.15 让球+1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>周二002</t>
+          <t>周三010</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>韩职</t>
+          <t>05-14 03:30</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>光州FCvs首尔FC</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>1.3</v>
+          <t>赫塔菲</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>马略卡</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>常规赛</t>
+        </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>2.06</t>
+          <t>SP2.20/3.20/3.50 让球-1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>周二003</t>
+          <t>周二001</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>05-12 18:30</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>塞尔塔vs莱万特</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>3.7</v>
+          <t>仁川联</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>浦项铁人</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>K1联赛</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>常规赛</t>
+        </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>3.18</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>1.86</t>
+          <t>SP3.10/2.62/2.55 让球-1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
+          <t>周二002</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>05-12 18:30</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>光州FC</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>FC首尔</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>K1联赛</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>常规赛</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>SP8.00/4.10/1.40 让球+2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 21:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>场次</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>联赛</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>主vs客</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>欧赔胜</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>欧赔平</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>欧赔负</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>让球数</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>竞彩SP胜</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>竞彩SP平</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>竞彩SP负</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>周二003</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>塞尔塔vs莱万特</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
           <t>周二004</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>沙特职业联赛</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>沙特联</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>利雅得胜利vs利雅得新月</t>
         </is>
       </c>
-      <c r="D26" s="7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="D34" s="7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>4.40</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>4.18</t>
         </is>
       </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>1.51</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>周二005</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>西甲</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>贝蒂斯vs埃尔切</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E27" s="6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F27" s="6" t="n">
+      <c r="D35" s="6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F35" s="6" t="n">
         <v>5.25</v>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>周二006</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>法乙</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>红星vs罗德兹</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>3.05</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>周二006</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>法甲</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>圣旺红星vs罗德兹</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>4.85</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>3.55</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>1.56</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>周二007</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>英冠</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>南安普敦vs米堡</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>4.70</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>3.94</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>周二008</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>奥萨苏纳vs马竞</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>5.55</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>🏆 今晚推荐（按场次顺序）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>场次</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>对阵</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>方向</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>信心</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>首选比分</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>备选比分</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>半全场</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>备选半全场</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>仓位</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>理由</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>周二001</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>仁川联vs浦项制铁</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>2/10</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>胜胜</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>平胜</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="J36" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=36%P平=32%P客=33%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球-1=输盘/让胜|赔变主↓59% 平↓18% 客↑89%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>周二002</t>
+          <t>周二007</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>光州FCvs首尔FC</t>
+          <t>英冠</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>2/10</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
+          <t>南安普顿vs米德尔斯堡</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>2.8</v>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>负负</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>平负</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="J37" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=31%P平=28%P客=41%|泊松比分0-1|半全场负负|大小球小2.5(40%)|让球+1=输盘/让胜|赔变主↑156% 平↑37% 客↓35%</t>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>1.51</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>周二003</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>塞尔塔vs莱万特</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>3/10</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>胜胜</t>
-        </is>
-      </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>平胜</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="J38" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=43%P平=28%P客=30%|泊松比分2-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜|赔变主↓44% 平↑17% 客↑132%</t>
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>周二008</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>奥萨苏纳vs马竞</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>5.55</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>1.43</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>周二004</t>
+          <t>周三001</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>利雅得胜利vs利雅得新月</t>
+          <t>日职</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>1/10</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
+          <t>神户胜利船vs京都不死鸟</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>4.75</v>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="J39" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=42%P平=29%P客=29%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球-1=输盘/让胜|赔变主↓41% 平↓6% 客↑60%</t>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>1.99</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>周二005</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>贝蒂斯vs埃尔切</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>3/10</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>胜胜</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>平胜</t>
-        </is>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="J40" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=49%P平=26%P客=25%|泊松比分3-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜|赔变主↓34% 平↑22% 客↑117%</t>
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>周三002</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>K1联赛</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>富川FCvs全北现代</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>3.38</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>周二006</t>
+          <t>周三003</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>圣旺红星vs罗德兹</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>3/10</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
+          <t>比利亚雷亚尔vs塞维利亚</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>3.75</v>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="J41" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=42%P平=30%P客=28%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球-1=输盘/让胜|赔变主↓56% 平↑7% 客↑109%</t>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>1.63</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>周二007</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>南安普敦vs米堡</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>2/10</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>胜胜</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>平胜</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="J42" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=44%P平=29%P客=27%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让胜|赔变主↓49% 平↓8% 客↑85%</t>
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>周三004</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>西班牙人vs毕尔巴鄂</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>5.60</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>周二008</t>
+          <t>周三005</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>奥萨苏纳vs马竞</t>
+          <t>法甲</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>3/10</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
+          <t>布雷斯特vs斯特拉斯堡</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>2.5</v>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="J43" s="8" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=40%P平=27%P客=33%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让胜|赔变主↓44% 平↓6% 客↑70%</t>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>4.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>周三006</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>英超</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>曼城vs水晶宫</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>周三007</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>意杯</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>拉齐奥vs国米</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>周三008</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>法甲</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>朗斯vs巴黎圣日耳曼</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>3.56</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>🏆 14场胜负彩+任选9（第26075期 停售2026-05-13 22:00）</t>
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>周三009</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>阿拉维斯vs巴萨</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>3.85</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>联赛</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>主队</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>客队</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>方向(双选)</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>周三010</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>赫塔菲vs马略卡</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>周二001</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>K1联赛</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>仁川联vs浦项铁人</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>9.25</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>周二002</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>K1联赛</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>光州FCvsFC首尔</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>🏆 今晚推荐（按场次顺序）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>场次</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>对阵</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>信心</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>胆材</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>首选比分</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>备选比分</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>半全场</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>备选半全场</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>仓位</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>理由</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>比赛日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>英超</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>曼彻斯特城</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>水晶宫</t>
-        </is>
-      </c>
-      <c r="E49" s="9" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F49" s="9" t="inlineStr">
-        <is>
-          <t>4.9/10</t>
-        </is>
-      </c>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>★胆</t>
-        </is>
-      </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>P主=49%</t>
-        </is>
-      </c>
-      <c r="J49" s="9" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>意大利杯</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>拉齐奥</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>国际米兰</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>客胜/平局</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>1/10</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>P主=32%P平=27%P客=41%</t>
-        </is>
-      </c>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>西班牙人</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>毕尔巴鄂竞技</t>
-        </is>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>4.1/10</t>
-        </is>
-      </c>
-      <c r="G51" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H51" s="9" t="inlineStr">
-        <is>
-          <t>★胆</t>
-        </is>
-      </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>P主=46%</t>
-        </is>
-      </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>比利亚雷亚尔</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>塞维利亚</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>3.7/10</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>P主=41%P平=28%P客=31%</t>
-        </is>
-      </c>
-      <c r="J52" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>阿拉维斯</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>巴塞罗那</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>客胜/平局</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>3.8/10</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>P主=31%P平=27%P客=42%</t>
-        </is>
-      </c>
-      <c r="J53" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>赫塔费</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>马洛卡</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>3.4/10</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>P主=38%P平=29%P客=33%</t>
-        </is>
-      </c>
-      <c r="J54" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>巴伦西亚</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>巴列卡诺</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>3.7/10</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>P主=41%P平=28%P客=31%</t>
-        </is>
-      </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>周二003</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>塞尔塔vs莱万特</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>赫罗纳</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>皇家社会</t>
+          <t>3/10</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>3.7/10</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>P主=41%P平=28%P客=32%</t>
-        </is>
-      </c>
-      <c r="J56" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=43%P平=28%P客=30%|泊松比分2-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜|赔变主↓44% 平↑17% 客↑132%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>周二004</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>利雅得胜利vs利雅得新月</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>皇家马德里</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>皇家奥维耶多</t>
+          <t>1/10</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>3.6/10</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>P主=40%P平=30%P客=30%</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J57" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=42%P平=28%P客=30%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球-1=输盘/让胜|赔变主↓41% 平↓6% 客↑60%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>周二005</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>法甲</t>
+          <t>贝蒂斯vs埃尔切</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>布雷斯特</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>斯特拉斯堡</t>
+          <t>3/10</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>3.5/10</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>P主=37%P平=28%P客=34%</t>
-        </is>
-      </c>
-      <c r="J58" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=49%P平=26%P客=25%|泊松比分3-1|半全场胜胜|大小球大2.5(69%)|让球-2=输盘/让胜|赔变主↓34% 平↑22% 客↑117%⚠️让-2深盘·主胜可能不穿盘</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>周二006</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>法甲</t>
+          <t>红星vs罗德兹</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>朗斯</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>巴黎圣日尔曼</t>
+          <t>3/10</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>3.6/10</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>P主=38%P平=29%P客=33%</t>
-        </is>
-      </c>
-      <c r="J59" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J59" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=42%P平=30%P客=28%|泊松比分1-0|半全场胜胜|大小球小2.5(41%)|让球-1=输盘/让胜|赔变主↓56% 平↑7% 客↑109%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>周二007</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>美职</t>
+          <t>南安普顿vs米德尔斯堡</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>辛辛那提FC</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>迈阿密国际</t>
+          <t>3/10</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>P主=39%P平=30%P客=30%</t>
-        </is>
-      </c>
-      <c r="J60" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J60" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=40%P平=29%P客=31%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球-1=输盘/让胜|赔变主↓49% 平↓8% 客↑85%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>周二008</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>美职</t>
+          <t>奥萨苏纳vs马竞</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>圣路易斯城</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>洛杉矶FC</t>
+          <t>3/10</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>胜胜</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>平胜</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>P主=39%P平=30%P客=30%</t>
-        </is>
-      </c>
-      <c r="J61" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J61" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=40%P平=26%P客=34%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让胜|赔变主↓44% 平↓6% 客↑70%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>周三001</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>美职</t>
+          <t>神户胜利船vs京都不死鸟</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>西雅图海湾人</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>圣何塞地震</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J62" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=46%P平=29%P客=26%|泊松比分2-0|半全场胜胜|大小球小2.5(44%)|让球-1=输盘/让胜</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>周三002</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>富川FCvs全北现代</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>P主=39%P平=30%P客=30%</t>
-        </is>
-      </c>
-      <c r="J62" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J63" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=32%P平=30%P客=38%|泊松比分0-1|半全场负负|大小球小2.5(40%)|让球+1=输盘/让胜</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>周三003</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>比利亚雷亚尔vs塞维利亚</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>负胜</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J64" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=44%P平=28%P客=28%|泊松比分3-2|半全场胜胜|大小球大2.5(71%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>📋 任选9方案（2胆+7双=128注=256元）</t>
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>周三004</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>西班牙人vs毕尔巴鄂</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J65" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=45%P平=27%P客=28%|泊松比分2-1|半全场胜胜|大小球大2.5(69%)|让球+1=走水/让平</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   1. 主胜           (信心4.9/10)</t>
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>周三005</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>布雷斯特vs斯特拉斯堡</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>负胜</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J66" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=37%P平=29%P客=34%|泊松比分2-1|半全场胜胜|大小球大2.5(68%)|让球+1=走水/让平</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   3. 主胜           (信心4.1/10)</t>
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>周三006</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>曼城vs水晶宫</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>5/10</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J67" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=58%P平=23%P客=20%|泊松比分4-1|半全场胜胜|大小球大2.5(71%)|让球-2=输盘/让胜⚠️让-2深盘·主胜可能不穿盘</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   5. 客胜/平局        (信心3.8/10)</t>
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>周三007</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>拉齐奥vs国米</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J68" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=29%P平=27%P客=44%|泊松比分1-3|半全场负负|大小球大2.5(70%)|让球+1=输盘/让胜</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   4. 主胜/平局        (信心3.7/10)</t>
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>周三008</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>朗斯vs巴黎圣日耳曼</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J69" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=34%P平=29%P客=37%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球+1=输盘/让胜</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   7. 主胜/平局        (信心3.7/10)</t>
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>周三009</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>阿拉维斯vs巴萨</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J70" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=32%P平=25%P客=43%|泊松比分1-4|半全场负负|大小球大2.5(72%)|让球+1=输盘/让胜</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   8. 主胜/平局        (信心3.7/10)</t>
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>周三010</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>赫塔菲vs马略卡</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J71" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=43%P平=29%P客=28%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球-1=输盘/让胜</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   9. 主胜/平局        (信心3.6/10)</t>
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>周二001</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>仁川联vs浦项铁人</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J72" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=36%P平=32%P客=32%|泊松比分1-0|半全场胜胜|大小球小2.5(41%)|让球-1=输盘/让胜|赔变主↓59% 平↓18% 客↑89%</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  11. 主胜/平局        (信心3.6/10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  10. 主胜/平局        (信心3.5/10)</t>
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>周二002</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>光州FCvsFC首尔</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="J73" s="8" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=30%P平=28%P客=41%|泊松比分0-1|半全场负负|大小球小2.5(39%)|让球+2=输盘/让胜|赔变主↑156% 平↑37% 客↓35%⚠️让+2深盘·客胜可能不穿盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>🏆 14场胜负彩+任选9（第26075期 停售2026-05-13 22:00）</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>方案</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>组合场次</t>
+          <t>联赛</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>每场选择</t>
+          <t>主队</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>注数</t>
+          <t>客队</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>金额</t>
+          <t>方向(双选)</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>综合SP</t>
+          <t>信心</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>说明</t>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>胆材</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>比赛日期</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>2串1</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>周二003+周二005</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>·塞尔塔:主胜(1.74)
-·贝蒂斯:主胜(1.44)</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>1.74×1.44=2.51</t>
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>英超</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>曼彻斯特城</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>水晶宫</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>4.9/10</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>★胆</t>
+        </is>
+      </c>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>P主=49%</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>3串1</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>周二003+周二005+周二006</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>意大利杯</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>·塞尔塔:主胜(1.74)
-·贝蒂斯:主胜(1.44)
-·圣旺红星:主胜(2.12)</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="n">
-        <v>1</v>
+          <t>拉齐奥</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>国际米兰</t>
+        </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>客胜/平局</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>1/10</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>1.74×1.44×2.12=5.31</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>P主=32%P平=27%P客=41%</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>西班牙人</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>毕尔巴鄂竞技</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>P主=45% 优势17%</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>比利亚雷亚尔</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>塞维利亚</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>P主=44% 优势16%</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>阿拉维斯</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>巴塞罗那</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>客胜/平局</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>3.8/10</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>P主=31%P平=27%P客=42%</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>赫塔费</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>马洛卡</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>3.4/10</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>P主=38%P平=29%P客=33%</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>巴伦西亚</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>巴列卡诺</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>3.7/10</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>P主=41%P平=28%P客=31%</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>赫罗纳</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>皇家社会</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>3.7/10</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>P主=41%P平=28%P客=32%</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>西甲</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>皇家马德里</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>皇家奥维耶多</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>3.6/10</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>P主=40%P平=30%P客=30%</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>法甲</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>布雷斯特</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>斯特拉斯堡</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>P主=37%P平=29%P客=34%</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>法甲</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>朗斯</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>巴黎圣日尔曼</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>3.6/10</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>P主=38%P平=29%P客=33%</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>美职</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>辛辛那提FC</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>迈阿密国际</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>P主=39%P平=30%P客=30%</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>美职</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>圣路易斯城</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>洛杉矶FC</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>P主=39%P平=30%P客=30%</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>美职</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>西雅图海湾人</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>圣何塞地震</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>主胜/平局</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>P主=39%P平=30%P客=30%</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>📋 任选9方案（1胆+8双=256注=512元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   1. 主胜           (信心4.9/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   5. 客胜/平局        (信心3.8/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   7. 主胜/平局        (信心3.7/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   8. 主胜/平局        (信心3.7/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   9. 主胜/平局        (信心3.6/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  11. 主胜/平局        (信心3.6/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   6. 主胜/平局        (信心3.4/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   3. 主胜           (信心3/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   4. 主胜           (信心3/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>方案</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>组合场次</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>每场选择</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>注数</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>综合SP</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>2串1</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>周三006+周二003</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>·曼城:主胜(1.20)
+·塞尔塔:主胜(1.85)</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>1.20×1.85=2.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>3串1</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>周三006+周二003+周二005</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>·曼城:主胜(1.20)
+·塞尔塔:主胜(1.85)
+·贝蒂斯:主胜(1.57)</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>3.49</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>1.20×1.85×1.57=3.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
           <t>4串1</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>周二003+周二005+周二006+周二008</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>·塞尔塔:主胜(1.74)
-·贝蒂斯:主胜(1.44)
-·圣旺红星:主胜(2.12)
-·奥萨苏纳:主胜(2.40)</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="n">
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>周三006+周二003+周二005+周二006</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>·曼城:主胜(1.20)
+·塞尔塔:主胜(1.85)
+·贝蒂斯:主胜(1.57)
+·红星:主胜(2.25)</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E111" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>12.75</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>1.74×1.44×2.12×2.40=12.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>7.84</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>1.20×1.85×1.57×2.25=7.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>5串1</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>周三006+周二003+周二005+周二006+周二007</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>·曼城:主胜(1.20)
+·塞尔塔:主胜(1.85)
+·贝蒂斯:主胜(1.57)
+·红星:主胜(2.25)
+·南安普顿:主胜(2.45)</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>19.21</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>1.20×1.85×1.57×2.25×2.45=19.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>6串1</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>周三006+周二003+周二005+周二006+周二007+周二008</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>·曼城:主胜(1.20)
+·塞尔塔:主胜(1.85)
+·贝蒂斯:主胜(1.57)
+·红星:主胜(2.25)
+·南安普顿:主胜(2.45)
+·奥萨苏纳:主胜(2.60)</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>1.20×1.85×1.57×2.25×2.45×2.60=49.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>⚠️ 核心信号</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>信号</t>
         </is>
       </c>
-      <c r="B86" s="5" t="inlineStr">
+      <c r="B118" s="5" t="inlineStr">
         <is>
           <t>场次</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C118" s="5" t="inlineStr">
         <is>
           <t>解读</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>应对</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="9" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
         <is>
           <t>🟢 高信心(4/10+)</t>
         </is>
       </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>0场贝叶斯概率最高</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>周三006</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>1场贝叶斯概率最高</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
         <is>
           <t>作胆材/串关核心</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="9" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
         <is>
           <t>🟢 让球SP真实数据</t>
         </is>
       </c>
-      <c r="B88" s="6" t="inlineStr">
+      <c r="B120" s="6" t="inlineStr">
         <is>
           <t>全部场次</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
+      <c r="C120" s="6" t="inlineStr">
         <is>
           <t>从500.com让球页提取，非估算</t>
         </is>
       </c>
-      <c r="D88" s="6" t="inlineStr">
+      <c r="D120" s="6" t="inlineStr">
         <is>
           <t>可用作让球分析</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="11" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="11" t="inlineStr">
         <is>
           <t>🟡 平局候选</t>
         </is>
       </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>周二001/周二006</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>周二006/周二001</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
         <is>
           <t>2场平局概率30%+</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="D121" s="6" t="inlineStr">
         <is>
           <t>双选或慎入</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="11" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="11" t="inlineStr">
         <is>
           <t>🟡 让球数真实</t>
         </is>
       </c>
-      <c r="B90" s="6" t="inlineStr">
+      <c r="B122" s="6" t="inlineStr">
         <is>
           <t>全部场次</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr">
+      <c r="C122" s="6" t="inlineStr">
         <is>
           <t>从500.com data-rangqiu提取</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="D122" s="6" t="inlineStr">
         <is>
           <t>让球分析可靠</t>
         </is>
@@ -3067,25 +4596,25 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A47:J47"/>
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A85:J85"/>
-    <mergeCell ref="A72:J72"/>
-    <mergeCell ref="A68:J68"/>
-    <mergeCell ref="A67:J67"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A73:J73"/>
+    <mergeCell ref="A97:J97"/>
+    <mergeCell ref="A100:J100"/>
+    <mergeCell ref="A96:J96"/>
+    <mergeCell ref="A102:J102"/>
+    <mergeCell ref="A117:J117"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A77:J77"/>
+    <mergeCell ref="A98:J98"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A103:J103"/>
     <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A70:J70"/>
-    <mergeCell ref="A69:J69"/>
-    <mergeCell ref="A65:J65"/>
-    <mergeCell ref="A66:J66"/>
-    <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A54:J54"/>
+    <mergeCell ref="A99:J99"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A95:J95"/>
+    <mergeCell ref="A101:J101"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A71:J71"/>
+    <mergeCell ref="A104:J104"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3097,7 +4626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3107,86 +4636,86 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>📋 2026-05-12 每场完整分析（8场）</t>
+          <t>📋 2026-05-12 每场完整分析（18场）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>⚽ 周二001 仁川联 vs 浦项制铁 [韩职] 18:30</t>
+          <t>⚽ 周二003 塞尔塔 vs 莱万特 [西甲] 05-13 01:00</t>
         </is>
       </c>
     </row>
     <row r="4" ht="130" customHeight="1">
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">时间：18:30
-联赛：韩职
-欧赔(spf)：3.2 / 2.6 / 2.32
-竞彩SP: 9.25/4.55/1.25
-差值分析：P主=36% P平=32% P客=33%
-推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
-让球:让-1 输盘=让胜 </t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>⚽ 周二002 光州FC vs 首尔FC [韩职] 18:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="130" customHeight="1">
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：18:30
-联赛：韩职
-欧赔(spf)：7.0 / 4.6 / 1.3
-竞彩SP: 2.82/3.45/2.06
-差值分析：P主=31% P平=28% P客=41%
-推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(40%) 备选半全场:平负
-让球:让+1 输盘=让胜 </t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>⚽ 周二003 塞尔塔 vs 莱万特 [西甲] 01:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="130" customHeight="1">
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：01:00
+          <t xml:space="preserve">时间：05-13 01:00
 联赛：西甲
-欧赔(spf)：1.74 / 3.52 / 3.7
-竞彩SP: 3.60/3.18/1.86
+欧赔(spf)：1.85 / 3.75 / 4.0
+竞彩SP: 1.87/3.87/4.23
 差值分析：P主=43% P平=28% P客=30%
 推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>⚽ 周二004 利雅得胜利 vs 利雅得新月 [沙特联] 05-13 02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="130" customHeight="1">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：05-13 02:00
+联赛：沙特联
+欧赔(spf)：2.2 / 3.4 / 2.88
+竞彩SP: 2.31/3.55/2.98
+差值分析：P主=42% P平=28% P客=30%
+推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
+让球:让-1 输盘=让胜 </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>⚽ 周二005 贝蒂斯 vs 埃尔切 [西甲] 05-13 02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="130" customHeight="1">
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>时间：05-13 02:00
+联赛：西甲
+欧赔(spf)：1.57 / 4.33 / 5.25
+竞彩SP: 1.61/4.40/5.34
+差值分析：P主=49% P平=26% P客=25%
+推荐：主胜 信心3/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
+让球:让-2 输盘=让胜 让-2深盘·主胜可能不穿盘</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>⚽ 周二004 利雅得胜利 vs 利雅得新月 [沙特职业联赛] 02:00</t>
+          <t>⚽ 周二006 红星 vs 罗德兹 [法乙] 05-13 02:30</t>
         </is>
       </c>
     </row>
     <row r="28" ht="130" customHeight="1">
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">时间：02:00
-联赛：沙特职业联赛
-欧赔(spf)：2.18 / 3.14 / 2.84
-竞彩SP: 4.40/4.18/1.51
-差值分析：P主=42% P平=29% P客=29%
-推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
+          <t xml:space="preserve">时间：05-13 02:30
+联赛：法乙
+欧赔(spf)：2.25 / 3.25 / 3.2
+竞彩SP: 2.26/3.48/3.24
+差值分析：P主=42% P平=30% P客=28%
+推荐：主胜 信心3/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(41%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
       </c>
@@ -3194,19 +4723,19 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>⚽ 周二005 贝蒂斯 vs 埃尔切 [西甲] 02:00</t>
+          <t>⚽ 周二007 南安普顿 vs 米德尔斯堡 [英冠] 05-13 03:00</t>
         </is>
       </c>
     </row>
     <row r="36" ht="130" customHeight="1">
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">时间：02:00
-联赛：西甲
-欧赔(spf)：1.44 / 4.1 / 5.25
-竞彩SP: 2.60/3.05/2.40
-差值分析：P主=49% P平=26% P客=25%
-推荐：主胜 信心3/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
+          <t xml:space="preserve">时间：05-13 03:00
+联赛：英冠
+欧赔(spf)：2.45 / 3.4 / 2.8
+竞彩SP: 2.54/3.40/2.90
+差值分析：P主=40% P平=29% P客=31%
+推荐：主胜 信心3/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
       </c>
@@ -3214,19 +4743,19 @@
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>⚽ 周二006 圣旺红星 vs 罗德兹 [法甲] 02:30</t>
+          <t>⚽ 周二008 奥萨苏纳 vs 马竞 [西甲] 05-13 03:30</t>
         </is>
       </c>
     </row>
     <row r="44" ht="130" customHeight="1">
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">时间：02:30
-联赛：法甲
-欧赔(spf)：2.12 / 2.8 / 3.34
-竞彩SP: 4.85/3.55/1.56
-差值分析：P主=42% P平=30% P客=28%
-推荐：主胜 信心3/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
+          <t xml:space="preserve">时间：05-13 03:30
+联赛：西甲
+欧赔(spf)：2.6 / 3.5 / 2.6
+竞彩SP: 2.62/3.63/2.70
+差值分析：P主=40% P平=26% P客=34%
+推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
       </c>
@@ -3234,19 +4763,19 @@
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>⚽ 周二007 南安普敦 vs 米堡 [英冠] 03:00</t>
+          <t>⚽ 周三001 神户胜利船 vs 京都不死鸟 [日职] 05-13 18:00</t>
         </is>
       </c>
     </row>
     <row r="52" ht="130" customHeight="1">
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">时间：03:00
-联赛：英冠
-欧赔(spf)：2.17 / 3.15 / 2.85
-竞彩SP: 4.70/3.94/1.51
-差值分析：P主=44% P平=29% P客=27%
-推荐：主胜 信心2/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
+          <t xml:space="preserve">时间：05-13 18:00
+联赛：日职
+欧赔(spf)：1.75 / 3.6 / 4.75
+竞彩SP: 1.78/3.66/4.86
+差值分析：P主=46% P平=29% P客=26%
+推荐：主胜 信心2/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
       </c>
@@ -3254,34 +4783,244 @@
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>⚽ 周二008 奥萨苏纳 vs 马竞 [西甲] 03:30</t>
+          <t>⚽ 周三002 富川FC vs 全北现代 [K1联赛] 05-13 18:30</t>
         </is>
       </c>
     </row>
     <row r="60" ht="130" customHeight="1">
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">时间：03:30
+          <t xml:space="preserve">时间：05-13 18:30
+联赛：K1联赛
+欧赔(spf)：4.33 / 3.4 / 1.75
+竞彩SP: 4.69/3.55/1.83
+差值分析：P主=32% P平=30% P客=38%
+推荐：客胜 信心1/10 比分0-1(泊松) 半全场负负 大小球小2.5(40%) 备选半全场:平负
+让球:让+1 输盘=让胜 </t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>⚽ 周三003 比利亚雷亚尔 vs 塞维利亚 [西甲] 05-14 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="130" customHeight="1">
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：05-14 01:00
 联赛：西甲
-欧赔(spf)：2.4 / 3.08 / 2.58
-竞彩SP: 5.55/4.00/1.43
-差值分析：P主=40% P平=27% P客=33%
-推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
+欧赔(spf)：2.05 / 3.3 / 3.75
+竞彩SP: 2.11/3.32/3.85
+差值分析：P主=44% P平=28% P客=28%
+推荐：主胜 信心3/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:负胜
 让球:让-1 输盘=让胜 </t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>⚽ 周三004 西班牙人 vs 毕尔巴鄂 [西甲] 05-14 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="130" customHeight="1">
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：05-14 01:00
+联赛：西甲
+欧赔(spf)：2.63 / 3.3 / 2.7
+竞彩SP: 2.72/3.26/2.79
+差值分析：P主=45% P平=27% P客=28%
+推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
+让球:让+1 走水=让平 </t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>⚽ 周三005 布雷斯特 vs 斯特拉斯堡 [法甲] 05-14 01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="130" customHeight="1">
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：05-14 01:00
+联赛：法甲
+欧赔(spf)：2.63 / 3.6 / 2.5
+竞彩SP: 2.76/3.62/2.53
+差值分析：P主=37% P平=29% P客=34%
+推荐：主胜 信心2/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(68%) 备选半全场:负胜
+让球:让+1 走水=让平 </t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="13" t="inlineStr">
+        <is>
+          <t>⚽ 周三006 曼城 vs 水晶宫 [英超] 05-14 03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="130" customHeight="1">
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>时间：05-14 03:00
+联赛：英超
+欧赔(spf)：1.2 / 7.5 / 12.0
+竞彩SP: 1.20/7.90/12.51
+差值分析：P主=58% P平=23% P客=20%
+推荐：主胜 信心5/10 比分4-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
+让球:让-2 输盘=让胜 让-2深盘·主胜可能不穿盘</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="13" t="inlineStr">
+        <is>
+          <t>⚽ 周三007 拉齐奥 vs 国米 [意杯] 05-14 03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="130" customHeight="1">
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：05-14 03:00
+联赛：意杯
+欧赔(spf)：5.25 / 3.9 / 1.62
+竞彩SP: 5.61/3.84/1.67
+差值分析：P主=29% P平=27% P客=44%
+推荐：客胜 信心1/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
+让球:让+1 输盘=让胜 </t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="13" t="inlineStr">
+        <is>
+          <t>⚽ 周三008 朗斯 vs 巴黎圣日耳曼 [法甲] 05-14 03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="130" customHeight="1">
+      <c r="B108" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：05-14 03:00
+联赛：法甲
+欧赔(spf)：3.4 / 4.0 / 1.95
+竞彩SP: 3.51/4.01/2.00
+差值分析：P主=34% P平=29% P客=37%
+推荐：客胜 信心3/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
+让球:让+1 输盘=让胜 </t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="13" t="inlineStr">
+        <is>
+          <t>⚽ 周三009 阿拉维斯 vs 巴萨 [西甲] 05-14 03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="130" customHeight="1">
+      <c r="B116" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：05-14 03:30
+联赛：西甲
+欧赔(spf)：3.1 / 3.75 / 2.15
+竞彩SP: 3.31/3.80/2.13
+差值分析：P主=32% P平=25% P客=43%
+推荐：客胜 信心3/10 比分1-4(泊松) 半全场负负 大小球大2.5(72%) 备选半全场:平负
+让球:让+1 输盘=让胜 </t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="13" t="inlineStr">
+        <is>
+          <t>⚽ 周三010 赫塔菲 vs 马略卡 [西甲] 05-14 03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="130" customHeight="1">
+      <c r="B124" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：05-14 03:30
+联赛：西甲
+欧赔(spf)：2.2 / 3.2 / 3.5
+竞彩SP: 2.26/3.21/3.59
+差值分析：P主=43% P平=29% P客=28%
+推荐：主胜 信心3/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
+让球:让-1 输盘=让胜 </t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="13" t="inlineStr">
+        <is>
+          <t>⚽ 周二001 仁川联 vs 浦项铁人 [K1联赛] 05-12 18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="130" customHeight="1">
+      <c r="B132" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：05-12 18:30
+联赛：K1联赛
+欧赔(spf)：3.1 / 2.62 / 2.55
+竞彩SP: 3.38/2.82/2.61
+差值分析：P主=36% P平=32% P客=32%
+推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(41%) 备选半全场:平胜
+让球:让-1 输盘=让胜 </t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="13" t="inlineStr">
+        <is>
+          <t>⚽ 周二002 光州FC vs FC首尔 [K1联赛] 05-12 18:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="130" customHeight="1">
+      <c r="B140" s="14" t="inlineStr">
+        <is>
+          <t>时间：05-12 18:30
+联赛：K1联赛
+欧赔(spf)：8.0 / 4.1 / 1.4
+竞彩SP: 7.88/4.70/1.43
+差值分析：P主=30% P平=28% P客=41%
+推荐：客胜 信心1/10 比分0-1(泊松) 半全场负负 大小球小2.5(39%) 备选半全场:平负
+让球:让+2 输盘=让胜 让+2深盘·客胜可能不穿盘</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="19">
     <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A139:B139"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="A131:B131"/>
+    <mergeCell ref="A35:B35"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A83:B83"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3293,7 +5032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3370,13 +5109,13 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>周二003+周二005</t>
+          <t>周三006+周二003</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>·塞尔塔:主胜(1.74)
-·贝蒂斯:主胜(1.44)</t>
+          <t>·曼城:主胜(1.20)
+·塞尔塔:主胜(1.85)</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
@@ -3384,7 +5123,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -3394,12 +5133,12 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>5元</t>
+          <t>4元</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>2.51倍</t>
+          <t>2.22倍</t>
         </is>
       </c>
     </row>
@@ -3411,14 +5150,14 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>周二003+周二005+周二006</t>
+          <t>周三006+周二003+周二005</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>·塞尔塔:主胜(1.74)
-·贝蒂斯:主胜(1.44)
-·圣旺红星:主胜(2.12)</t>
+          <t>·曼城:主胜(1.20)
+·塞尔塔:主胜(1.85)
+·贝蒂斯:主胜(1.57)</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
@@ -3426,7 +5165,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -3436,12 +5175,12 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>11元</t>
+          <t>7元</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>5.31倍</t>
+          <t>3.49倍</t>
         </is>
       </c>
     </row>
@@ -3453,15 +5192,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>周二003+周二005+周二006+周二008</t>
+          <t>周三006+周二003+周二005+周二006</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>·塞尔塔:主胜(1.74)
-·贝蒂斯:主胜(1.44)
-·圣旺红星:主胜(2.12)
-·奥萨苏纳:主胜(2.40)</t>
+          <t>·曼城:主胜(1.20)
+·塞尔塔:主胜(1.85)
+·贝蒂斯:主胜(1.57)
+·红星:主胜(2.25)</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
@@ -3469,7 +5208,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -3479,12 +5218,101 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>26元</t>
+          <t>16元</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>12.75倍</t>
+          <t>7.84倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>5串1</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>周三006+周二003+周二005+周二006+周二007</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>·曼城:主胜(1.20)
+·塞尔塔:主胜(1.85)
+·贝蒂斯:主胜(1.57)
+·红星:主胜(2.25)
+·南安普顿:主胜(2.45)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>19.21</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>38元</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>19.21倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>6串1</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>周三006+周二003+周二005+周二006+周二007+周二008</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>·曼城:主胜(1.20)
+·塞尔塔:主胜(1.85)
+·贝蒂斯:主胜(1.57)
+·红星:主胜(2.25)
+·南安普顿:主胜(2.45)
+·奥萨苏纳:主胜(2.60)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>2元</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>100元</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>49.95倍</t>
         </is>
       </c>
     </row>
@@ -3508,7 +5336,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二005</t>
+          <t>周三006+周二003</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
@@ -3516,7 +5344,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>63.00</t>
+          <t>56.00</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -3526,12 +5354,12 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>63元</t>
+          <t>56元</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>63.00倍</t>
+          <t>56.00倍</t>
         </is>
       </c>
     </row>
@@ -3548,7 +5376,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二005+周二006</t>
+          <t>周三006+周二003+周二005</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
@@ -3556,7 +5384,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>664.00</t>
+          <t>436.00</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -3566,12 +5394,12 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>664元</t>
+          <t>436元</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>664.00倍</t>
+          <t>436.00倍</t>
         </is>
       </c>
     </row>
@@ -3602,7 +5430,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二005+周二006</t>
+          <t>周三006+周二003+周二005</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
@@ -3610,7 +5438,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -3620,12 +5448,12 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>5元</t>
+          <t>3元</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>5.31倍</t>
+          <t>3.49倍</t>
         </is>
       </c>
     </row>
@@ -3642,7 +5470,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二005+周二006+周二008</t>
+          <t>周三006+周二003+周二005+周二006</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
@@ -3650,7 +5478,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -3660,21 +5488,28 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>13元</t>
+          <t>8元</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>12.75倍</t>
+          <t>7.84倍</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>D. 半全场串关（从泊松比分推半全场）</t>
         </is>
       </c>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="17" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -3689,7 +5524,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二005</t>
+          <t>周三006+周二003</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
@@ -3729,7 +5564,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二005+周二006</t>
+          <t>周三006+周二003+周二005</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
@@ -3769,7 +5604,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>周二003+周二005+周二006+周二008</t>
+          <t>周三006+周二003+周二005+周二006</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
@@ -3793,6 +5628,86 @@
       <c r="H18" s="6" t="inlineStr">
         <is>
           <t>23.43倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>5串1</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>半全场</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>周三006+周二003+周二005+周二006+周二007</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>51.54</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>1元</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>52元</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>51.54倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>6串1</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>半全场</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>周三006+周二003+周二005+周二006+周二007+周二008</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>113.38</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>1元</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>113元</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>113.38倍</t>
         </is>
       </c>
     </row>

--- a/Aii竞彩推荐_2026-05-12.xlsx
+++ b/Aii竞彩推荐_2026-05-12.xlsx
@@ -593,7 +593,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 21:19</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 21:27</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 21:19</t>
+          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 21:27</t>
         </is>
       </c>
     </row>

--- a/Aii竞彩推荐_2026-05-12.xlsx
+++ b/Aii竞彩推荐_2026-05-12.xlsx
@@ -593,7 +593,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 21:27</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 21:43</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP1.57/4.33/5.25 让球-2</t>
+          <t>SP1.57/4.33/5.25 让球-1</t>
         </is>
       </c>
     </row>
@@ -1507,14 +1507,14 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>SP8.00/4.10/1.40 让球+2</t>
+          <t>SP8.00/4.10/1.40 让球+1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 21:27</t>
+          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 21:43</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="J58" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=49%P平=26%P客=25%|泊松比分3-1|半全场胜胜|大小球大2.5(69%)|让球-2=输盘/让胜|赔变主↓34% 平↑22% 客↑117%⚠️让-2深盘·主胜可能不穿盘</t>
+          <t>贝叶斯P主=49%P平=26%P客=25%|泊松比分3-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜|赔变主↓34% 平↑22% 客↑117%</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="J73" s="8" t="inlineStr">
         <is>
-          <t>贝叶斯P主=30%P平=28%P客=41%|泊松比分0-1|半全场负负|大小球小2.5(39%)|让球+2=输盘/让胜|赔变主↑156% 平↑37% 客↓35%⚠️让+2深盘·客胜可能不穿盘</t>
+          <t>贝叶斯P主=30%P平=28%P客=41%|泊松比分0-1|半全场负负|大小球小2.5(39%)|让球+1=输盘/让胜|赔变主↑156% 平↑37% 客↓35%</t>
         </is>
       </c>
     </row>
@@ -3557,104 +3557,104 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="inlineStr">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B81" s="9" t="inlineStr">
         <is>
           <t>西甲</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C81" s="9" t="inlineStr">
         <is>
           <t>西班牙人</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D81" s="9" t="inlineStr">
         <is>
           <t>毕尔巴鄂竞技</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E81" s="9" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>3/10</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
         <is>
           <t>2.63</t>
         </is>
       </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>★胆</t>
+        </is>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
         <is>
           <t>P主=45% 优势17%</t>
         </is>
       </c>
-      <c r="J81" s="6" t="inlineStr">
+      <c r="J81" s="9" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
+      <c r="A82" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B82" s="9" t="inlineStr">
         <is>
           <t>西甲</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C82" s="9" t="inlineStr">
         <is>
           <t>比利亚雷亚尔</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D82" s="9" t="inlineStr">
         <is>
           <t>塞维利亚</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E82" s="9" t="inlineStr">
         <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>3/10</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
         <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>★胆</t>
+        </is>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
         <is>
           <t>P主=44% 优势16%</t>
         </is>
       </c>
-      <c r="J82" s="6" t="inlineStr">
+      <c r="J82" s="9" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
@@ -4183,7 +4183,7 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>📋 任选9方案（1胆+8双=256注=512元）</t>
+          <t>📋 任选9方案（3胆+6双=64注=128元）</t>
         </is>
       </c>
     </row>
@@ -4197,56 +4197,56 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   5. 客胜/平局        (信心3.8/10)</t>
+          <t xml:space="preserve">   3. 主胜           (信心4/10)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   7. 主胜/平局        (信心3.7/10)</t>
+          <t xml:space="preserve">   4. 主胜           (信心4/10)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   8. 主胜/平局        (信心3.7/10)</t>
+          <t xml:space="preserve">   5. 客胜/平局        (信心3.8/10)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   9. 主胜/平局        (信心3.6/10)</t>
+          <t xml:space="preserve">   7. 主胜/平局        (信心3.7/10)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11. 主胜/平局        (信心3.6/10)</t>
+          <t xml:space="preserve">   8. 主胜/平局        (信心3.7/10)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   6. 主胜/平局        (信心3.4/10)</t>
+          <t xml:space="preserve">   9. 主胜/平局        (信心3.6/10)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   3. 主胜           (信心3/10)</t>
+          <t xml:space="preserve">  11. 主胜/平局        (信心3.6/10)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   4. 主胜           (信心3/10)</t>
+          <t xml:space="preserve">   6. 主胜/平局        (信心3.4/10)</t>
         </is>
       </c>
     </row>
@@ -4295,13 +4295,13 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>周三006+周二003</t>
+          <t>周三006+周二005</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
           <t>·曼城:主胜(1.20)
-·塞尔塔:主胜(1.85)</t>
+·贝蒂斯:主胜(1.57)</t>
         </is>
       </c>
       <c r="D109" s="6" t="n">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>1.20×1.85=2.22</t>
+          <t>1.20×1.57=1.88</t>
         </is>
       </c>
     </row>
@@ -4331,14 +4331,14 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>周三006+周二003+周二005</t>
+          <t>周三006+周二005+周三003</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
           <t>·曼城:主胜(1.20)
-·塞尔塔:主胜(1.85)
-·贝蒂斯:主胜(1.57)</t>
+·贝蒂斯:主胜(1.57)
+·比利亚雷亚尔:主胜(2.05)</t>
         </is>
       </c>
       <c r="D110" s="6" t="n">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>1.20×1.85×1.57=3.49</t>
+          <t>1.20×1.57×2.05=3.86</t>
         </is>
       </c>
     </row>
@@ -4368,15 +4368,15 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>周三006+周二003+周二005+周二006</t>
+          <t>周三006+周二005+周三003+周三004</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
           <t>·曼城:主胜(1.20)
-·塞尔塔:主胜(1.85)
 ·贝蒂斯:主胜(1.57)
-·红星:主胜(2.25)</t>
+·比利亚雷亚尔:主胜(2.05)
+·西班牙人:主胜(2.63)</t>
         </is>
       </c>
       <c r="D111" s="6" t="n">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>1.20×1.85×1.57×2.25=7.84</t>
+          <t>1.20×1.57×2.05×2.63=10.16</t>
         </is>
       </c>
     </row>
@@ -4406,16 +4406,16 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>周三006+周二003+周二005+周二006+周二007</t>
+          <t>周三006+周二005+周三003+周三004+周三008</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
           <t>·曼城:主胜(1.20)
-·塞尔塔:主胜(1.85)
 ·贝蒂斯:主胜(1.57)
-·红星:主胜(2.25)
-·南安普顿:主胜(2.45)</t>
+·比利亚雷亚尔:主胜(2.05)
+·西班牙人:主胜(2.63)
+·朗斯:客胜(1.95)</t>
         </is>
       </c>
       <c r="D112" s="6" t="n">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>19.81</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>1.20×1.85×1.57×2.25×2.45=19.21</t>
+          <t>1.20×1.57×2.05×2.63×1.95=19.81</t>
         </is>
       </c>
     </row>
@@ -4445,17 +4445,17 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>周三006+周二003+周二005+周二006+周二007+周二008</t>
+          <t>周三006+周二005+周三003+周三004+周三008+周三009</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
           <t>·曼城:主胜(1.20)
-·塞尔塔:主胜(1.85)
 ·贝蒂斯:主胜(1.57)
-·红星:主胜(2.25)
-·南安普顿:主胜(2.45)
-·奥萨苏纳:主胜(2.60)</t>
+·比利亚雷亚尔:主胜(2.05)
+·西班牙人:主胜(2.63)
+·朗斯:客胜(1.95)
+·阿拉维斯:客胜(2.15)</t>
         </is>
       </c>
       <c r="D113" s="6" t="n">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>1.20×1.85×1.57×2.25×2.45×2.60=49.95</t>
+          <t>1.20×1.57×2.05×2.63×1.95×2.15=42.59</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>周三006</t>
+          <t>周二005/周三003/周三004/周三006/周三008</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>1场贝叶斯概率最高</t>
+          <t>7场贝叶斯概率最高</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
@@ -4690,13 +4690,13 @@
     <row r="20" ht="130" customHeight="1">
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>时间：05-13 02:00
+          <t xml:space="preserve">时间：05-13 02:00
 联赛：西甲
 欧赔(spf)：1.57 / 4.33 / 5.25
 竞彩SP: 1.61/4.40/5.34
 差值分析：P主=49% P平=26% P客=25%
-推荐：主胜 信心3/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
-让球:让-2 输盘=让胜 让-2深盘·主胜可能不穿盘</t>
+推荐：主胜 信心4/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
+让球:让-1 输盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
 欧赔(spf)：2.05 / 3.3 / 3.75
 竞彩SP: 2.11/3.32/3.85
 差值分析：P主=44% P平=28% P客=28%
-推荐：主胜 信心3/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:负胜
+推荐：主胜 信心4/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:负胜
 让球:让-1 输盘=让胜 </t>
         </is>
       </c>
@@ -4835,7 +4835,7 @@
 欧赔(spf)：2.63 / 3.3 / 2.7
 竞彩SP: 2.72/3.26/2.79
 差值分析：P主=45% P平=27% P客=28%
-推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
+推荐：主胜 信心4/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
 让球:让+1 走水=让平 </t>
         </is>
       </c>
@@ -4875,7 +4875,7 @@
 欧赔(spf)：1.2 / 7.5 / 12.0
 竞彩SP: 1.20/7.90/12.51
 差值分析：P主=58% P平=23% P客=20%
-推荐：主胜 信心5/10 比分4-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
+推荐：主胜 信心6/10 比分4-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
 让球:让-2 输盘=让胜 让-2深盘·主胜可能不穿盘</t>
         </is>
       </c>
@@ -4915,7 +4915,7 @@
 欧赔(spf)：3.4 / 4.0 / 1.95
 竞彩SP: 3.51/4.01/2.00
 差值分析：P主=34% P平=29% P客=37%
-推荐：客胜 信心3/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
+推荐：客胜 信心4/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
 让球:让+1 输盘=让胜 </t>
         </is>
       </c>
@@ -4935,7 +4935,7 @@
 欧赔(spf)：3.1 / 3.75 / 2.15
 竞彩SP: 3.31/3.80/2.13
 差值分析：P主=32% P平=25% P客=43%
-推荐：客胜 信心3/10 比分1-4(泊松) 半全场负负 大小球大2.5(72%) 备选半全场:平负
+推荐：客胜 信心4/10 比分1-4(泊松) 半全场负负 大小球大2.5(72%) 备选半全场:平负
 让球:让+1 输盘=让胜 </t>
         </is>
       </c>
@@ -4955,7 +4955,7 @@
 欧赔(spf)：2.2 / 3.2 / 3.5
 竞彩SP: 2.26/3.21/3.59
 差值分析：P主=43% P平=29% P客=28%
-推荐：主胜 信心3/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
+推荐：主胜 信心4/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
 让球:让-1 输盘=让胜 </t>
         </is>
       </c>
@@ -4990,13 +4990,13 @@
     <row r="140" ht="130" customHeight="1">
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>时间：05-12 18:30
+          <t xml:space="preserve">时间：05-12 18:30
 联赛：K1联赛
 欧赔(spf)：8.0 / 4.1 / 1.4
 竞彩SP: 7.88/4.70/1.43
 差值分析：P主=30% P平=28% P客=41%
 推荐：客胜 信心1/10 比分0-1(泊松) 半全场负负 大小球小2.5(39%) 备选半全场:平负
-让球:让+2 输盘=让胜 让+2深盘·客胜可能不穿盘</t>
+让球:让+1 输盘=让胜 </t>
         </is>
       </c>
     </row>
@@ -5109,13 +5109,13 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>周三006+周二003</t>
+          <t>周三006+周二005</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
           <t>·曼城:主胜(1.20)
-·塞尔塔:主胜(1.85)</t>
+·贝蒂斯:主胜(1.57)</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>2.22倍</t>
+          <t>1.88倍</t>
         </is>
       </c>
     </row>
@@ -5150,14 +5150,14 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>周三006+周二003+周二005</t>
+          <t>周三006+周二005+周三003</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
           <t>·曼城:主胜(1.20)
-·塞尔塔:主胜(1.85)
-·贝蒂斯:主胜(1.57)</t>
+·贝蒂斯:主胜(1.57)
+·比利亚雷亚尔:主胜(2.05)</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>7元</t>
+          <t>8元</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>3.49倍</t>
+          <t>3.86倍</t>
         </is>
       </c>
     </row>
@@ -5192,15 +5192,15 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>周三006+周二003+周二005+周二006</t>
+          <t>周三006+周二005+周三003+周三004</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
           <t>·曼城:主胜(1.20)
-·塞尔塔:主胜(1.85)
 ·贝蒂斯:主胜(1.57)
-·红星:主胜(2.25)</t>
+·比利亚雷亚尔:主胜(2.05)
+·西班牙人:主胜(2.63)</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>16元</t>
+          <t>20元</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>7.84倍</t>
+          <t>10.16倍</t>
         </is>
       </c>
     </row>
@@ -5235,16 +5235,16 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>周三006+周二003+周二005+周二006+周二007</t>
+          <t>周三006+周二005+周三003+周三004+周三008</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
           <t>·曼城:主胜(1.20)
-·塞尔塔:主胜(1.85)
 ·贝蒂斯:主胜(1.57)
-·红星:主胜(2.25)
-·南安普顿:主胜(2.45)</t>
+·比利亚雷亚尔:主胜(2.05)
+·西班牙人:主胜(2.63)
+·朗斯:客胜(1.95)</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>19.81</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -5262,12 +5262,12 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>38元</t>
+          <t>40元</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>19.21倍</t>
+          <t>19.81倍</t>
         </is>
       </c>
     </row>
@@ -5279,17 +5279,17 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>周三006+周二003+周二005+周二006+周二007+周二008</t>
+          <t>周三006+周二005+周三003+周三004+周三008+周三009</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
           <t>·曼城:主胜(1.20)
-·塞尔塔:主胜(1.85)
 ·贝蒂斯:主胜(1.57)
-·红星:主胜(2.25)
-·南安普顿:主胜(2.45)
-·奥萨苏纳:主胜(2.60)</t>
+·比利亚雷亚尔:主胜(2.05)
+·西班牙人:主胜(2.63)
+·朗斯:客胜(1.95)
+·阿拉维斯:客胜(2.15)</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -5307,12 +5307,12 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>100元</t>
+          <t>85元</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>49.95倍</t>
+          <t>42.59倍</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>周三006+周二003</t>
+          <t>周三006+周二005</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>56.00</t>
+          <t>47.00</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>56元</t>
+          <t>47元</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>56.00倍</t>
+          <t>47.00倍</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>周三006+周二003+周二005</t>
+          <t>周三006+周二005+周三003</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>436.00</t>
+          <t>483.00</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -5394,12 +5394,12 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>436元</t>
+          <t>483元</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>436.00倍</t>
+          <t>483.00倍</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>周三006+周二003+周二005</t>
+          <t>周三006+周二005+周三003</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>3元</t>
+          <t>4元</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>3.49倍</t>
+          <t>3.86倍</t>
         </is>
       </c>
     </row>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>周三006+周二003+周二005+周二006</t>
+          <t>周三006+周二005+周三003+周三004</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>8元</t>
+          <t>10元</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>7.84倍</t>
+          <t>10.16倍</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>周三006+周二003</t>
+          <t>周三006+周二005</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>周三006+周二003+周二005</t>
+          <t>周三006+周二005+周三003</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>周三006+周二003+周二005+周二006</t>
+          <t>周三006+周二005+周三003+周三004</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>周三006+周二003+周二005+周二006+周二007</t>
+          <t>周三006+周二005+周三003+周三004+周三008</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>51.54</t>
+          <t>58.56</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -5662,12 +5662,12 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>52元</t>
+          <t>59元</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>51.54倍</t>
+          <t>58.56倍</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>周三006+周二003+周二005+周二006+周二007+周二008</t>
+          <t>周三006+周二005+周三003+周三004+周三008+周三009</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>113.38</t>
+          <t>146.41</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>113元</t>
+          <t>146元</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>113.38倍</t>
+          <t>146.41倍</t>
         </is>
       </c>
     </row>
